--- a/2026/GAEBELER 1949/Marzo/Marzo Gaebeler.xlsx
+++ b/2026/GAEBELER 1949/Marzo/Marzo Gaebeler.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistemax\Desktop\rc-consorcio2025\2026\GAEBELER 1949\Febrero\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\2026\GAEBELER 1949\Marzo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{218D85FA-5E3D-4645-97F9-43529032F0FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31B77347-9ECD-4647-A10D-63B0A37FBB8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="850" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="850" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="1" r:id="rId1"/>
@@ -19,20 +19,15 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="2">Edesur!$A$1:$M$27</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">PRORRATEO!$A$1:$O$26</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$E$85</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">PRORRATEO!$A$1:$N$26</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$E$79</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
-  <extLst>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="99">
   <si>
     <t>UF</t>
   </si>
@@ -298,18 +293,6 @@
     <t>LUNES A VIERNES 10 A 15HS</t>
   </si>
   <si>
-    <t>VTO 20/03</t>
-  </si>
-  <si>
-    <t>Seguro integral de cosorcio - Federacion patronal - Poliza 2217080 - Enero</t>
-  </si>
-  <si>
-    <t>Seguro integral de cosorcio - Federacion patronal - Poliza 2217080 - Febrero</t>
-  </si>
-  <si>
-    <t>Edesur</t>
-  </si>
-  <si>
     <t>Chida Gustavo Daniel</t>
   </si>
   <si>
@@ -319,9 +302,6 @@
     <t>Graciela Vigamonti</t>
   </si>
   <si>
-    <t>PREVISION ORDINARIA DE CAJA PARA ABONO DE EDESUR</t>
-  </si>
-  <si>
     <t>SALDO INICIAL</t>
   </si>
   <si>
@@ -329,6 +309,21 @@
   </si>
   <si>
     <t>Hugo Britez Ramon Irala</t>
+  </si>
+  <si>
+    <t>Plan de pago Anticipo edesur</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Seguro integral de cosorcio - Federacion patronal - Poliza 2217080 </t>
+  </si>
+  <si>
+    <t>Transferencia no identificada Sra. Antonela Borgia 20/03</t>
+  </si>
+  <si>
+    <t>VTO 06/04</t>
+  </si>
+  <si>
+    <t>PREVISION ORDINARIA DE CAJA</t>
   </si>
 </sst>
 </file>
@@ -347,7 +342,7 @@
     <numFmt numFmtId="169" formatCode="_-&quot;$&quot;\ * #,##0.00_-;\-&quot;$&quot;\ * #,##0.00_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@"/>
     <numFmt numFmtId="170" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="31" x14ac:knownFonts="1">
+  <fonts count="32" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -562,6 +557,13 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="13">
     <fill>
@@ -637,7 +639,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="41">
+  <borders count="40">
     <border>
       <left/>
       <right/>
@@ -888,17 +890,6 @@
       </right>
       <top/>
       <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom style="thin">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
@@ -1123,7 +1114,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="222">
+  <cellXfs count="218">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1216,10 +1207,10 @@
     <xf numFmtId="165" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="14" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="14" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="18" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="18" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="18" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="18" fillId="0" borderId="26" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="18" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1238,7 +1229,7 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="44" fontId="4" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="44" fontId="19" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1250,14 +1241,10 @@
     <xf numFmtId="44" fontId="10" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="44" fontId="9" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="44" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1271,10 +1258,10 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="166" fontId="14" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="2" fillId="10" borderId="25" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="2" fillId="10" borderId="24" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -1296,7 +1283,6 @@
     <xf numFmtId="44" fontId="3" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="6" fillId="4" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="19" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="14" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1307,51 +1293,51 @@
     <xf numFmtId="168" fontId="22" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="169" fontId="24" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="22" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="22" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="22" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="22" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="23" fillId="11" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="11" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="11" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="11" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="11" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="11" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="11" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="168" fontId="26" fillId="11" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="11" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="168" fontId="26" fillId="11" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="11" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="27" fillId="2" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="2" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="43" fontId="12" fillId="2" borderId="1" xfId="4" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="28" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="27" fillId="2" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="28" fillId="2" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="27" fillId="2" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="169" fontId="27" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="27" fillId="2" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="27" fillId="2" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="22" fillId="9" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="9" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1360,25 +1346,25 @@
     <xf numFmtId="43" fontId="12" fillId="2" borderId="2" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="27" fillId="2" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="27" fillId="2" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="169" fontId="27" fillId="2" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="27" fillId="2" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="169" fontId="27" fillId="2" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="27" fillId="0" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="169" fontId="27" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="168" fontId="27" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="169" fontId="27" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="27" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="170" fontId="22" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="22" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="169" fontId="22" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="170" fontId="22" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="22" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="169" fontId="22" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="169" fontId="22" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="169" fontId="27" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="169" fontId="27" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="168" fontId="22" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="23" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -1388,30 +1374,30 @@
     <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="44" fontId="2" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="43" fontId="12" fillId="2" borderId="2" xfId="4" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="26" fillId="11" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="11" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="169" fontId="27" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="169" fontId="27" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="169" fontId="29" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="169" fontId="27" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="2" fillId="4" borderId="40" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="2" fillId="4" borderId="39" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="170" fontId="27" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="170" fontId="27" fillId="0" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="18" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="18" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="10" fillId="8" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="9" fillId="6" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1444,68 +1430,63 @@
     <xf numFmtId="0" fontId="17" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="14" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="22" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="22" fillId="0" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="12" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="169" fontId="25" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="25" fillId="0" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="44" fontId="31" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Millares 2" xfId="4" xr:uid="{769376F3-FA42-4CBE-8FC6-971888C358BE}"/>
@@ -1586,9 +1567,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1626,9 +1607,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1661,26 +1642,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1713,26 +1677,9 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1906,21 +1853,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M89"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:M83"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="37.5703125" customWidth="1"/>
-    <col min="2" max="2" width="24.7109375" customWidth="1"/>
-    <col min="3" max="3" width="15.85546875" hidden="1" customWidth="1"/>
-    <col min="4" max="4" width="21.7109375" customWidth="1"/>
-    <col min="5" max="5" width="14.7109375" customWidth="1"/>
+    <col min="1" max="1" width="37.5546875" customWidth="1"/>
+    <col min="2" max="2" width="24.6640625" customWidth="1"/>
+    <col min="3" max="3" width="15.88671875" hidden="1" customWidth="1"/>
+    <col min="4" max="4" width="21.6640625" customWidth="1"/>
+    <col min="5" max="5" width="14.6640625" customWidth="1"/>
     <col min="6" max="6" width="13" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5546875" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="18" customWidth="1"/>
-    <col min="12" max="12" width="18.28515625" customWidth="1"/>
+    <col min="12" max="12" width="18.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="15"/>
       <c r="B1" s="60" t="s">
         <v>68</v>
@@ -1929,25 +1876,25 @@
       <c r="D1" s="60"/>
       <c r="E1" s="61"/>
     </row>
-    <row r="2" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="16"/>
-      <c r="B2" s="192" t="s">
+      <c r="B2" s="189" t="s">
         <v>19</v>
       </c>
-      <c r="C2" s="192"/>
-      <c r="D2" s="192"/>
-      <c r="E2" s="193"/>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C2" s="189"/>
+      <c r="D2" s="189"/>
+      <c r="E2" s="190"/>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" s="16"/>
-      <c r="B3" s="179" t="s">
+      <c r="B3" s="176" t="s">
         <v>25</v>
       </c>
       <c r="C3" s="17"/>
       <c r="D3" s="17"/>
       <c r="E3" s="18"/>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="16"/>
       <c r="B4" s="17" t="s">
         <v>84</v>
@@ -1956,67 +1903,67 @@
       <c r="D4" s="17"/>
       <c r="E4" s="18"/>
     </row>
-    <row r="5" spans="1:5" ht="35.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="180" t="s">
+    <row r="5" spans="1:5" ht="35.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="177" t="s">
         <v>83</v>
       </c>
-      <c r="B5" s="181"/>
-      <c r="C5" s="181"/>
-      <c r="D5" s="181" t="s">
+      <c r="B5" s="178"/>
+      <c r="C5" s="178"/>
+      <c r="D5" s="178" t="s">
         <v>87</v>
       </c>
-      <c r="E5" s="182"/>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B7" s="199" t="s">
-        <v>88</v>
-      </c>
-      <c r="C7" s="199"/>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B8" s="199"/>
-      <c r="C8" s="199"/>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B9" s="199"/>
-      <c r="C9" s="199"/>
-    </row>
-    <row r="12" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="198" t="s">
+      <c r="E5" s="179"/>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B7" s="196" t="s">
+        <v>97</v>
+      </c>
+      <c r="C7" s="196"/>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B8" s="196"/>
+      <c r="C8" s="196"/>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B9" s="196"/>
+      <c r="C9" s="196"/>
+    </row>
+    <row r="12" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="195" t="s">
         <v>28</v>
       </c>
-      <c r="B12" s="198"/>
-      <c r="C12" s="198"/>
-      <c r="D12" s="198"/>
-      <c r="E12" s="198"/>
-    </row>
-    <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="198"/>
-      <c r="B13" s="198"/>
-      <c r="C13" s="198"/>
-      <c r="D13" s="198"/>
-      <c r="E13" s="198"/>
-    </row>
-    <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="198"/>
-      <c r="B14" s="198"/>
-      <c r="C14" s="198"/>
-      <c r="D14" s="198"/>
-      <c r="E14" s="198"/>
-    </row>
-    <row r="15" spans="1:5" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="198"/>
-      <c r="B15" s="198"/>
-      <c r="C15" s="198"/>
-      <c r="D15" s="198"/>
-      <c r="E15" s="198"/>
-    </row>
-    <row r="16" spans="1:5" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="17" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+      <c r="B12" s="195"/>
+      <c r="C12" s="195"/>
+      <c r="D12" s="195"/>
+      <c r="E12" s="195"/>
+    </row>
+    <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="195"/>
+      <c r="B13" s="195"/>
+      <c r="C13" s="195"/>
+      <c r="D13" s="195"/>
+      <c r="E13" s="195"/>
+    </row>
+    <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="195"/>
+      <c r="B14" s="195"/>
+      <c r="C14" s="195"/>
+      <c r="D14" s="195"/>
+      <c r="E14" s="195"/>
+    </row>
+    <row r="15" spans="1:5" ht="53.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="195"/>
+      <c r="B15" s="195"/>
+      <c r="C15" s="195"/>
+      <c r="D15" s="195"/>
+      <c r="E15" s="195"/>
+    </row>
+    <row r="16" spans="1:5" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="17" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A17" s="2"/>
     </row>
-    <row r="18" spans="1:7" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" s="11" t="s">
         <v>5</v>
       </c>
@@ -2025,86 +1972,84 @@
       <c r="D19" s="9"/>
       <c r="E19" s="14"/>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" s="31" t="s">
         <v>81</v>
       </c>
-      <c r="B20" s="113"/>
-      <c r="C20" s="113"/>
-      <c r="D20" s="114"/>
-      <c r="E20" s="115"/>
-    </row>
-    <row r="21" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="190" t="s">
-        <v>89</v>
-      </c>
-      <c r="B21" s="191"/>
+      <c r="B20" s="111"/>
+      <c r="C20" s="111"/>
+      <c r="D20" s="112"/>
+      <c r="E20" s="113"/>
+    </row>
+    <row r="21" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="187" t="s">
+        <v>95</v>
+      </c>
+      <c r="B21" s="188"/>
       <c r="C21" s="5"/>
-      <c r="D21" s="186">
+      <c r="D21" s="183">
         <v>52745</v>
       </c>
-      <c r="E21" s="117"/>
-    </row>
-    <row r="22" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="190" t="s">
-        <v>90</v>
-      </c>
-      <c r="B22" s="191"/>
+      <c r="E21" s="115"/>
+    </row>
+    <row r="22" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="187" t="s">
+        <v>94</v>
+      </c>
+      <c r="B22" s="188"/>
       <c r="C22" s="5"/>
-      <c r="D22" s="186">
-        <v>52745</v>
-      </c>
-      <c r="E22" s="117"/>
-    </row>
-    <row r="23" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D22" s="183">
+        <v>496816.96</v>
+      </c>
+      <c r="E22" s="115"/>
+    </row>
+    <row r="23" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A23" s="26" t="s">
         <v>82</v>
       </c>
       <c r="B23" s="26"/>
       <c r="C23" s="26"/>
-      <c r="D23" s="178"/>
-      <c r="E23" s="112">
+      <c r="D23" s="175"/>
+      <c r="E23" s="110">
         <f>SUM(D21:D22)</f>
-        <v>105490</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+        <v>549561.96</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" s="26" t="s">
         <v>4</v>
       </c>
       <c r="B24" s="31"/>
       <c r="C24" s="31"/>
       <c r="D24" s="31"/>
-      <c r="E24" s="116">
+      <c r="E24" s="114">
         <f>E23</f>
-        <v>105490</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>549561.96</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A25" s="5"/>
       <c r="B25" s="5"/>
       <c r="C25" s="5"/>
       <c r="D25" s="78"/>
       <c r="E25" s="84"/>
     </row>
-    <row r="26" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A26" s="27" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="B26" s="27"/>
       <c r="C26" s="27"/>
       <c r="D26" s="85"/>
-      <c r="E26" s="188">
-        <v>1000000</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E26" s="185"/>
+    </row>
+    <row r="27" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A27" s="1"/>
       <c r="D27" s="86"/>
       <c r="E27" s="87"/>
       <c r="F27" s="39"/>
     </row>
-    <row r="28" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A28" s="3" t="s">
         <v>7</v>
       </c>
@@ -2113,20 +2058,20 @@
       <c r="D28" s="88"/>
       <c r="E28" s="89">
         <f>E24+E26</f>
-        <v>1105490</v>
-      </c>
-      <c r="F28" s="111"/>
+        <v>549561.96</v>
+      </c>
+      <c r="F28" s="109"/>
       <c r="G28" s="39"/>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="D29" s="86"/>
       <c r="E29" s="86"/>
     </row>
-    <row r="30" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D30" s="86"/>
       <c r="E30" s="86"/>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31" s="11" t="s">
         <v>30</v>
       </c>
@@ -2135,35 +2080,35 @@
       <c r="D31" s="90"/>
       <c r="E31" s="91"/>
     </row>
-    <row r="32" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="190"/>
-      <c r="B32" s="191"/>
+    <row r="32" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="187"/>
+      <c r="B32" s="188"/>
       <c r="C32" s="5"/>
-      <c r="D32" s="100"/>
+      <c r="D32" s="98"/>
       <c r="E32" s="79"/>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A33" s="190"/>
-      <c r="B33" s="191"/>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A33" s="187"/>
+      <c r="B33" s="188"/>
       <c r="C33" s="5"/>
       <c r="D33" s="81"/>
       <c r="E33" s="79"/>
     </row>
-    <row r="34" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="196"/>
-      <c r="B34" s="197"/>
+    <row r="34" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="193"/>
+      <c r="B34" s="194"/>
       <c r="C34" s="5"/>
       <c r="D34" s="81"/>
       <c r="E34" s="79"/>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A35" s="80"/>
       <c r="B35" s="82"/>
       <c r="C35" s="5"/>
       <c r="D35" s="81"/>
       <c r="E35" s="79"/>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A36" s="45"/>
       <c r="B36" s="44"/>
       <c r="C36" s="44"/>
@@ -2173,9 +2118,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="38" spans="1:5" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="39" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="38" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="39" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A39" s="27" t="s">
         <v>10</v>
       </c>
@@ -2184,8 +2129,8 @@
       <c r="D39" s="28"/>
       <c r="E39" s="77"/>
     </row>
-    <row r="40" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="41" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="41" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A41" s="3" t="s">
         <v>11</v>
       </c>
@@ -2197,26 +2142,26 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="43" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="43" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A43" s="75" t="s">
         <v>8</v>
       </c>
       <c r="B43" s="76">
         <f>E28</f>
-        <v>1105490</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>549561.96</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A44" s="75" t="s">
         <v>9</v>
       </c>
       <c r="B44" s="76">
         <f>E28-E26</f>
-        <v>105490</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>549561.96</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A45" s="75" t="s">
         <v>12</v>
       </c>
@@ -2225,7 +2170,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A46" s="75" t="s">
         <v>26</v>
       </c>
@@ -2234,93 +2179,93 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:5" ht="73.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="48" spans="1:5" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="49" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="194"/>
-      <c r="B49" s="194"/>
-      <c r="C49" s="194"/>
-      <c r="D49" s="194"/>
-      <c r="E49" s="194"/>
-    </row>
-    <row r="50" spans="1:6" ht="106.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="194"/>
-      <c r="B50" s="194"/>
-      <c r="C50" s="194"/>
-      <c r="D50" s="194"/>
-      <c r="E50" s="194"/>
-    </row>
-    <row r="51" spans="1:6" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="194"/>
-      <c r="B51" s="194"/>
-      <c r="C51" s="194"/>
-      <c r="D51" s="194"/>
-      <c r="E51" s="194"/>
-    </row>
-    <row r="53" spans="1:6" ht="0.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:5" ht="73.5" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="48" spans="1:5" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="49" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A49" s="191"/>
+      <c r="B49" s="191"/>
+      <c r="C49" s="191"/>
+      <c r="D49" s="191"/>
+      <c r="E49" s="191"/>
+    </row>
+    <row r="50" spans="1:6" ht="106.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A50" s="191"/>
+      <c r="B50" s="191"/>
+      <c r="C50" s="191"/>
+      <c r="D50" s="191"/>
+      <c r="E50" s="191"/>
+    </row>
+    <row r="51" spans="1:6" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A51" s="191"/>
+      <c r="B51" s="191"/>
+      <c r="C51" s="191"/>
+      <c r="D51" s="191"/>
+      <c r="E51" s="191"/>
+    </row>
+    <row r="53" spans="1:6" ht="0.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="20" t="s">
         <v>22</v>
       </c>
-      <c r="B53" s="97"/>
+      <c r="B53" s="95"/>
       <c r="C53" s="21"/>
     </row>
-    <row r="54" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A54" s="30"/>
       <c r="B54" s="52">
         <v>0</v>
       </c>
       <c r="C54" s="23"/>
     </row>
-    <row r="55" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="22" t="s">
         <v>2</v>
       </c>
       <c r="B55" s="36">
         <f>PRORRATEO!F25</f>
-        <v>236613.83</v>
+        <v>986668.29</v>
       </c>
       <c r="C55" s="21"/>
     </row>
-    <row r="56" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A56" s="22"/>
       <c r="B56" s="36">
         <v>0</v>
       </c>
       <c r="C56" s="21"/>
     </row>
-    <row r="57" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A57" s="22" t="s">
         <v>27</v>
       </c>
       <c r="B57" s="83">
-        <f>B84</f>
-        <v>0</v>
+        <f>B78</f>
+        <v>165459</v>
       </c>
       <c r="C57" s="21"/>
     </row>
-    <row r="58" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A58" s="25"/>
       <c r="B58" s="43"/>
       <c r="C58" s="21"/>
     </row>
-    <row r="59" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="96" t="s">
+    <row r="59" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A59" s="94" t="s">
         <v>31</v>
       </c>
       <c r="B59" s="43"/>
       <c r="C59" s="21"/>
     </row>
-    <row r="60" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A60" s="35" t="s">
         <v>13</v>
       </c>
       <c r="B60" s="43">
         <f>-B44</f>
-        <v>-105490</v>
+        <v>-549561.96</v>
       </c>
       <c r="C60" s="21"/>
     </row>
-    <row r="61" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A61" s="25" t="s">
         <v>14</v>
       </c>
@@ -2330,216 +2275,174 @@
       </c>
       <c r="C61" s="21"/>
     </row>
-    <row r="62" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A62" s="29" t="s">
         <v>4</v>
       </c>
       <c r="B62" s="52">
         <f>SUM(B54:B61)</f>
-        <v>131123.82999999999</v>
+        <v>602565.33000000007</v>
       </c>
       <c r="C62" s="24"/>
       <c r="D62" s="39"/>
     </row>
-    <row r="63" spans="1:6" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:6" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B63" s="37"/>
       <c r="C63" s="24"/>
       <c r="D63" s="39"/>
-      <c r="E63" s="98"/>
-      <c r="F63" s="99"/>
-    </row>
-    <row r="64" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E63" s="96"/>
+      <c r="F63" s="97"/>
+    </row>
+    <row r="64" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B64" s="38"/>
       <c r="C64" s="24"/>
     </row>
-    <row r="65" spans="1:4" s="34" customFormat="1" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:13" s="34" customFormat="1" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A65"/>
       <c r="B65" s="37"/>
       <c r="C65" s="33"/>
     </row>
-    <row r="66" spans="1:4" s="34" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A66" s="102" t="s">
-        <v>96</v>
-      </c>
-      <c r="B66" s="189">
-        <v>-345093.76999999996</v>
+    <row r="66" spans="1:13" s="34" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A66" s="100" t="s">
+        <v>91</v>
+      </c>
+      <c r="B66" s="186">
+        <v>-2735183.96</v>
       </c>
       <c r="C66" s="33"/>
       <c r="D66" s="42"/>
     </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A67" s="48" t="s">
         <v>34</v>
       </c>
-      <c r="B67" s="183">
+      <c r="B67" s="180">
         <f>-B44</f>
-        <v>-105490</v>
-      </c>
-    </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
+        <v>-549561.96</v>
+      </c>
+    </row>
+    <row r="68" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A68" s="48" t="s">
         <v>35</v>
       </c>
-      <c r="B68" s="107">
+      <c r="B68" s="105">
         <f>-B45</f>
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A69" s="48" t="s">
         <v>39</v>
       </c>
-      <c r="B69" s="107">
-        <f>B84</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B69" s="105">
+        <f>B78</f>
+        <v>165459</v>
+      </c>
+      <c r="D69" s="39">
+        <f>B69+B70</f>
+        <v>1152127.29</v>
+      </c>
+    </row>
+    <row r="70" spans="1:13" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A70" s="48" t="s">
-        <v>91</v>
-      </c>
-      <c r="B70" s="183">
-        <f>-310242.6</f>
-        <v>-310242.59999999998</v>
-      </c>
-    </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A71" s="48" t="s">
-        <v>91</v>
-      </c>
-      <c r="B71" s="183">
-        <f>-544144.19</f>
-        <v>-544144.18999999994</v>
-      </c>
-    </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A72" s="48" t="s">
-        <v>91</v>
-      </c>
-      <c r="B72" s="183">
-        <f>-555834.79</f>
-        <v>-555834.79</v>
-      </c>
-    </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A73" s="48" t="s">
-        <v>91</v>
-      </c>
-      <c r="B73" s="183">
-        <v>-452185.43</v>
-      </c>
-    </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A74" s="48" t="s">
-        <v>91</v>
-      </c>
-      <c r="B74" s="183">
-        <v>-658807.01</v>
-      </c>
-      <c r="D74" s="39"/>
-    </row>
-    <row r="75" spans="1:4" ht="13.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A75" s="48" t="s">
         <v>36</v>
       </c>
-      <c r="B75" s="108">
+      <c r="B70" s="106">
         <f>PRORRATEO!F25</f>
-        <v>236613.83</v>
-      </c>
-    </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A76" s="109" t="s">
+        <v>986668.29</v>
+      </c>
+    </row>
+    <row r="71" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A71" s="107" t="s">
         <v>37</v>
       </c>
-      <c r="B76" s="110"/>
-    </row>
-    <row r="77" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A77" s="105" t="s">
+      <c r="B71" s="108"/>
+    </row>
+    <row r="72" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A72" s="103" t="s">
         <v>32</v>
       </c>
-      <c r="B77" s="106">
-        <f>SUM(B66:C76)</f>
-        <v>-2735183.96</v>
-      </c>
-    </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A78" s="103"/>
-      <c r="B78" s="103"/>
-    </row>
-    <row r="79" spans="1:4" ht="34.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A80" s="195" t="s">
+      <c r="B72" s="104">
+        <f>SUM(B66:C71)</f>
+        <v>-2132618.63</v>
+      </c>
+    </row>
+    <row r="73" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A73" s="101"/>
+      <c r="B73" s="101"/>
+    </row>
+    <row r="74" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="75" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A75" s="192" t="s">
         <v>21</v>
       </c>
-      <c r="B80" s="195"/>
-      <c r="C80" s="195"/>
-    </row>
-    <row r="81" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A81" s="195"/>
-      <c r="B81" s="195"/>
-      <c r="C81" s="195"/>
-    </row>
-    <row r="82" spans="1:13" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A82" s="93"/>
-      <c r="B82" s="32"/>
-      <c r="C82" s="32">
+      <c r="B75" s="192"/>
+      <c r="C75" s="192"/>
+    </row>
+    <row r="76" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A76" s="192"/>
+      <c r="B76" s="192"/>
+      <c r="C76" s="192"/>
+    </row>
+    <row r="77" spans="1:13" ht="35.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A77" s="92" t="s">
+        <v>96</v>
+      </c>
+      <c r="B77" s="32">
+        <v>165459</v>
+      </c>
+      <c r="C77" s="32">
         <v>40000</v>
       </c>
-      <c r="E82" s="111"/>
-    </row>
-    <row r="83" spans="1:13" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A83" s="93"/>
-      <c r="B83" s="95"/>
-      <c r="C83" s="92"/>
-      <c r="D83" s="111"/>
-    </row>
-    <row r="84" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A84" s="40" t="s">
+      <c r="E77" s="109"/>
+    </row>
+    <row r="78" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A78" s="40" t="s">
         <v>4</v>
       </c>
-      <c r="B84" s="94">
-        <f>SUM(B82:B83)</f>
-        <v>0</v>
-      </c>
-      <c r="C84" s="41"/>
-    </row>
-    <row r="85" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="M85" s="8"/>
-    </row>
-    <row r="86" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A86" s="194"/>
-      <c r="B86" s="194"/>
-      <c r="C86" s="194"/>
-      <c r="D86" s="194"/>
-      <c r="E86" s="194"/>
-    </row>
-    <row r="87" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A87" s="194"/>
-      <c r="B87" s="194"/>
-      <c r="C87" s="194"/>
-      <c r="D87" s="194"/>
-      <c r="E87" s="194"/>
-    </row>
-    <row r="88" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A88" s="194"/>
-      <c r="B88" s="194"/>
-      <c r="C88" s="194"/>
-      <c r="D88" s="194"/>
-      <c r="E88" s="194"/>
-    </row>
-    <row r="89" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A89" s="194"/>
-      <c r="B89" s="194"/>
-      <c r="C89" s="194"/>
-      <c r="D89" s="194"/>
-      <c r="E89" s="194"/>
+      <c r="B78" s="93">
+        <f>SUM(B77:B77)</f>
+        <v>165459</v>
+      </c>
+      <c r="C78" s="41"/>
+    </row>
+    <row r="79" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="M79" s="8"/>
+    </row>
+    <row r="80" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A80" s="191"/>
+      <c r="B80" s="191"/>
+      <c r="C80" s="191"/>
+      <c r="D80" s="191"/>
+      <c r="E80" s="191"/>
+    </row>
+    <row r="81" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A81" s="191"/>
+      <c r="B81" s="191"/>
+      <c r="C81" s="191"/>
+      <c r="D81" s="191"/>
+      <c r="E81" s="191"/>
+    </row>
+    <row r="82" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A82" s="191"/>
+      <c r="B82" s="191"/>
+      <c r="C82" s="191"/>
+      <c r="D82" s="191"/>
+      <c r="E82" s="191"/>
+    </row>
+    <row r="83" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A83" s="191"/>
+      <c r="B83" s="191"/>
+      <c r="C83" s="191"/>
+      <c r="D83" s="191"/>
+      <c r="E83" s="191"/>
     </row>
   </sheetData>
   <mergeCells count="11">
     <mergeCell ref="A22:B22"/>
     <mergeCell ref="B2:E2"/>
-    <mergeCell ref="A86:E89"/>
-    <mergeCell ref="A80:C81"/>
+    <mergeCell ref="A80:E83"/>
+    <mergeCell ref="A75:C76"/>
     <mergeCell ref="A49:E51"/>
     <mergeCell ref="A33:B33"/>
     <mergeCell ref="A32:B32"/>
@@ -2556,30 +2459,29 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:R30"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:Q30"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="4.28515625" customWidth="1"/>
-    <col min="2" max="2" width="18.5703125" customWidth="1"/>
-    <col min="3" max="3" width="0.140625" customWidth="1"/>
-    <col min="4" max="4" width="8.42578125" customWidth="1"/>
-    <col min="5" max="5" width="14.140625" customWidth="1"/>
-    <col min="6" max="6" width="12.28515625" customWidth="1"/>
-    <col min="7" max="7" width="7.7109375" hidden="1" customWidth="1"/>
-    <col min="8" max="8" width="10.5703125" customWidth="1"/>
-    <col min="9" max="9" width="9.5703125" customWidth="1"/>
-    <col min="10" max="10" width="0.140625" customWidth="1"/>
-    <col min="11" max="11" width="12.42578125" customWidth="1"/>
-    <col min="12" max="12" width="10.42578125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.7109375" customWidth="1"/>
-    <col min="14" max="14" width="0.42578125" hidden="1" customWidth="1"/>
-    <col min="15" max="15" width="14.28515625" customWidth="1"/>
-    <col min="16" max="16" width="7.140625" hidden="1" customWidth="1"/>
-    <col min="17" max="17" width="12" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="13" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="4.33203125" customWidth="1"/>
+    <col min="2" max="2" width="18.5546875" customWidth="1"/>
+    <col min="3" max="3" width="0.109375" customWidth="1"/>
+    <col min="4" max="4" width="8.44140625" customWidth="1"/>
+    <col min="5" max="5" width="14.109375" customWidth="1"/>
+    <col min="6" max="6" width="12.33203125" customWidth="1"/>
+    <col min="7" max="7" width="7.6640625" hidden="1" customWidth="1"/>
+    <col min="8" max="8" width="10.5546875" customWidth="1"/>
+    <col min="9" max="9" width="9.5546875" customWidth="1"/>
+    <col min="10" max="10" width="0.109375" customWidth="1"/>
+    <col min="11" max="11" width="12.44140625" customWidth="1"/>
+    <col min="12" max="12" width="14.6640625" customWidth="1"/>
+    <col min="13" max="13" width="0.44140625" hidden="1" customWidth="1"/>
+    <col min="14" max="14" width="14.33203125" customWidth="1"/>
+    <col min="15" max="15" width="7.109375" hidden="1" customWidth="1"/>
+    <col min="16" max="16" width="12" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:17" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="6"/>
       <c r="B1" s="17" t="str">
         <f>RESUMEN!B4</f>
@@ -2597,173 +2499,159 @@
       <c r="L1" s="6"/>
       <c r="M1" s="6"/>
       <c r="N1" s="6"/>
-      <c r="O1" s="6"/>
-    </row>
-    <row r="2" spans="1:18" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:17" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="6"/>
-      <c r="B2" s="206" t="s">
+      <c r="B2" s="197" t="s">
         <v>86</v>
       </c>
-      <c r="C2" s="206"/>
-      <c r="D2" s="206"/>
-      <c r="E2" s="206"/>
-      <c r="F2" s="206"/>
-      <c r="G2" s="206"/>
-      <c r="H2" s="206"/>
+      <c r="C2" s="197"/>
+      <c r="D2" s="197"/>
+      <c r="E2" s="197"/>
+      <c r="F2" s="197"/>
+      <c r="G2" s="197"/>
+      <c r="H2" s="197"/>
       <c r="I2" s="6"/>
       <c r="J2" s="7"/>
       <c r="K2" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="L2" s="6"/>
-      <c r="M2" s="101">
+      <c r="L2" s="99">
         <v>1105490</v>
       </c>
+      <c r="M2" s="49"/>
       <c r="N2" s="49"/>
-      <c r="O2" s="49"/>
-      <c r="P2" s="19"/>
-    </row>
-    <row r="3" spans="1:18" ht="12.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="O2" s="19"/>
+    </row>
+    <row r="3" spans="1:17" ht="12.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="6"/>
-      <c r="B3" s="207"/>
-      <c r="C3" s="207"/>
-      <c r="D3" s="207"/>
-      <c r="E3" s="207"/>
-      <c r="F3" s="207"/>
-      <c r="G3" s="207"/>
-      <c r="H3" s="207"/>
+      <c r="B3" s="198"/>
+      <c r="C3" s="198"/>
+      <c r="D3" s="198"/>
+      <c r="E3" s="198"/>
+      <c r="F3" s="198"/>
+      <c r="G3" s="198"/>
+      <c r="H3" s="198"/>
       <c r="I3" s="6"/>
       <c r="J3" s="6"/>
       <c r="K3" s="6"/>
-      <c r="L3" s="6"/>
+      <c r="L3" s="50"/>
       <c r="M3" s="50"/>
-      <c r="N3" s="50"/>
-      <c r="O3" s="53"/>
-    </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A4" s="200" t="s">
-        <v>0</v>
-      </c>
-      <c r="B4" s="200" t="s">
+      <c r="N3" s="53"/>
+    </row>
+    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A4" s="201" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4" s="201" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="200" t="s">
+      <c r="C4" s="201" t="s">
         <v>17</v>
       </c>
-      <c r="D4" s="200" t="s">
+      <c r="D4" s="201" t="s">
         <v>6</v>
       </c>
-      <c r="E4" s="202" t="s">
+      <c r="E4" s="205" t="s">
         <v>33</v>
       </c>
-      <c r="F4" s="200" t="s">
+      <c r="F4" s="201" t="s">
         <v>2</v>
       </c>
-      <c r="G4" s="200" t="s">
+      <c r="G4" s="201" t="s">
         <v>18</v>
       </c>
-      <c r="H4" s="204" t="s">
+      <c r="H4" s="209" t="s">
         <v>20</v>
       </c>
-      <c r="I4" s="202" t="s">
+      <c r="I4" s="205" t="s">
         <v>29</v>
       </c>
-      <c r="J4" s="202" t="s">
+      <c r="J4" s="205" t="s">
         <v>3</v>
       </c>
-      <c r="K4" s="202" t="s">
+      <c r="K4" s="205" t="s">
         <v>16</v>
       </c>
-      <c r="L4" s="214" t="s">
-        <v>91</v>
-      </c>
-      <c r="M4" s="56" t="s">
+      <c r="L4" s="56" t="s">
         <v>24</v>
       </c>
-      <c r="N4" s="211" t="s">
+      <c r="M4" s="203" t="s">
         <v>15</v>
       </c>
-      <c r="O4" s="208" t="s">
+      <c r="N4" s="199" t="s">
         <v>23</v>
       </c>
-      <c r="R4" s="39"/>
-    </row>
-    <row r="5" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="201"/>
-      <c r="B5" s="201"/>
-      <c r="C5" s="210"/>
-      <c r="D5" s="201"/>
-      <c r="E5" s="203"/>
-      <c r="F5" s="201"/>
-      <c r="G5" s="210"/>
-      <c r="H5" s="205"/>
-      <c r="I5" s="203"/>
-      <c r="J5" s="213"/>
-      <c r="K5" s="203"/>
-      <c r="L5" s="215"/>
-      <c r="M5" s="54" t="str">
+      <c r="Q4" s="39"/>
+    </row>
+    <row r="5" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="208"/>
+      <c r="B5" s="208"/>
+      <c r="C5" s="202"/>
+      <c r="D5" s="208"/>
+      <c r="E5" s="207"/>
+      <c r="F5" s="208"/>
+      <c r="G5" s="202"/>
+      <c r="H5" s="210"/>
+      <c r="I5" s="207"/>
+      <c r="J5" s="206"/>
+      <c r="K5" s="207"/>
+      <c r="L5" s="54" t="str">
         <f>RESUMEN!B7</f>
-        <v>VTO 20/03</v>
-      </c>
-      <c r="N5" s="212"/>
-      <c r="O5" s="209"/>
-    </row>
-    <row r="6" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+        <v>VTO 06/04</v>
+      </c>
+      <c r="M5" s="204"/>
+      <c r="N5" s="200"/>
+    </row>
+    <row r="6" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="57" t="s">
         <v>44</v>
       </c>
       <c r="B6" s="57" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="C6" s="57"/>
-      <c r="D6" s="120">
+      <c r="D6" s="117">
         <f>8+1.02777778</f>
         <v>9.027777780000001</v>
       </c>
       <c r="E6" s="63">
-        <v>32089.01</v>
-      </c>
-      <c r="F6" s="187">
-        <f>E6</f>
-        <v>32089.01</v>
-      </c>
+        <v>260082.01</v>
+      </c>
+      <c r="F6" s="217"/>
       <c r="G6" s="64"/>
       <c r="H6" s="65">
         <f>E6-F6</f>
-        <v>0</v>
+        <v>260082.01</v>
       </c>
       <c r="I6" s="65">
         <f>IF(H6&gt;0,H6*3%,0)</f>
-        <v>0</v>
+        <v>7802.4602999999997</v>
       </c>
       <c r="J6" s="66">
         <v>0</v>
       </c>
       <c r="K6" s="67">
-        <f>M$2*D6/100</f>
+        <f>L$2*D6/100</f>
         <v>99801.180580122003</v>
       </c>
-      <c r="L6" s="118">
-        <f>Edesur!M5</f>
-        <v>160281.11988019495</v>
-      </c>
-      <c r="M6" s="68">
-        <f>ROUND(SUM(H6:L6),0) + P6</f>
-        <v>260082.01</v>
-      </c>
-      <c r="N6" s="69">
-        <f>ROUND(M6*6% + M6,0) + P6</f>
-        <v>275687.01</v>
-      </c>
-      <c r="O6" s="70">
-        <f>ROUND(M6*3%,0) + M6</f>
-        <v>267884.01</v>
-      </c>
-      <c r="P6" s="39">
+      <c r="L6" s="68">
+        <f>ROUND(SUM(H6:K6),0) + O6</f>
+        <v>367686.01</v>
+      </c>
+      <c r="M6" s="69">
+        <f>ROUND(L6*6% + L6,0) + O6</f>
+        <v>389747.01</v>
+      </c>
+      <c r="N6" s="70">
+        <f>ROUND(L6*3%,0) + L6</f>
+        <v>378717.01</v>
+      </c>
+      <c r="O6" s="39">
         <v>0.01</v>
       </c>
     </row>
-    <row r="7" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="57" t="s">
         <v>45</v>
       </c>
@@ -2771,16 +2659,16 @@
         <v>40</v>
       </c>
       <c r="C7" s="58"/>
-      <c r="D7" s="120">
+      <c r="D7" s="117">
         <f>1.02777778+4.9</f>
         <v>5.9277777800000004</v>
       </c>
       <c r="E7" s="63">
-        <v>20456.02</v>
-      </c>
-      <c r="F7" s="187">
+        <v>241298.02</v>
+      </c>
+      <c r="F7" s="184">
         <f>E7</f>
-        <v>20456.02</v>
+        <v>241298.02</v>
       </c>
       <c r="G7" s="64"/>
       <c r="H7" s="65">
@@ -2795,34 +2683,30 @@
         <v>0</v>
       </c>
       <c r="K7" s="67">
-        <f t="shared" ref="K7:K24" si="2">M$2*D7%</f>
+        <f>L$2*D7%</f>
         <v>65530.990580122008</v>
       </c>
-      <c r="L7" s="118">
-        <f>Edesur!M6</f>
-        <v>175767.15626019496</v>
-      </c>
-      <c r="M7" s="68">
-        <f t="shared" ref="M7:M24" si="3">ROUND(SUM(H7:L7),0) + P7</f>
-        <v>241298.02</v>
-      </c>
-      <c r="N7" s="69">
-        <f t="shared" ref="N7:N24" si="4">ROUND(M7*6% + M7,0) + P7</f>
-        <v>255776.02</v>
-      </c>
-      <c r="O7" s="70">
-        <f t="shared" ref="O7:O24" si="5">ROUND(M7*3%,0) + M7</f>
-        <v>248537.02</v>
-      </c>
-      <c r="P7" s="39">
-        <f>P6+0.01</f>
+      <c r="L7" s="68">
+        <f>ROUND(SUM(H7:K7),0) + O7</f>
+        <v>65531.02</v>
+      </c>
+      <c r="M7" s="69">
+        <f t="shared" ref="M7:M24" si="2">ROUND(L7*6% + L7,0) + O7</f>
+        <v>69463.02</v>
+      </c>
+      <c r="N7" s="70">
+        <f t="shared" ref="N7:N24" si="3">ROUND(L7*3%,0) + L7</f>
+        <v>67497.01999999999</v>
+      </c>
+      <c r="O7" s="39">
+        <f>O6+0.01</f>
         <v>0.02</v>
       </c>
-      <c r="Q7" s="39" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="8" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="P7" s="39" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="57" t="s">
         <v>47</v>
       </c>
@@ -2830,16 +2714,15 @@
         <v>41</v>
       </c>
       <c r="C8" s="58"/>
-      <c r="D8" s="120">
+      <c r="D8" s="117">
         <f>1.02777778+3.2</f>
         <v>4.2277777800000003</v>
       </c>
-      <c r="E8" s="63">
-        <v>15028.03</v>
-      </c>
-      <c r="F8" s="187">
-        <f>E8</f>
-        <v>15028.03</v>
+      <c r="E8" s="184">
+        <v>200808.03</v>
+      </c>
+      <c r="F8" s="184">
+        <v>200808.03</v>
       </c>
       <c r="G8" s="64"/>
       <c r="H8" s="65">
@@ -2854,31 +2737,27 @@
         <v>0</v>
       </c>
       <c r="K8" s="67">
+        <f>L$2*D8%</f>
+        <v>46737.660580121999</v>
+      </c>
+      <c r="L8" s="68">
+        <f>ROUND(SUM(H8:K8),0) + O8</f>
+        <v>46738.03</v>
+      </c>
+      <c r="M8" s="69">
         <f t="shared" si="2"/>
-        <v>46737.660580121999</v>
-      </c>
-      <c r="L8" s="118">
-        <f>Edesur!M7</f>
-        <v>148221.01492019495</v>
-      </c>
-      <c r="M8" s="68">
+        <v>49542.03</v>
+      </c>
+      <c r="N8" s="70">
         <f t="shared" si="3"/>
-        <v>194959.03</v>
-      </c>
-      <c r="N8" s="69">
-        <f t="shared" si="4"/>
-        <v>206657.03</v>
-      </c>
-      <c r="O8" s="70">
-        <f t="shared" si="5"/>
-        <v>200808.03</v>
-      </c>
-      <c r="P8" s="39">
-        <f t="shared" ref="P8:P24" si="6">P7+0.01</f>
+        <v>48140.03</v>
+      </c>
+      <c r="O8" s="39">
+        <f t="shared" ref="O8:O24" si="4">O7+0.01</f>
         <v>0.03</v>
       </c>
     </row>
-    <row r="9" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="57" t="s">
         <v>48</v>
       </c>
@@ -2886,53 +2765,49 @@
         <v>42</v>
       </c>
       <c r="C9" s="58"/>
-      <c r="D9" s="120">
+      <c r="D9" s="117">
         <f>8+1.02777778</f>
         <v>9.027777780000001</v>
       </c>
       <c r="E9" s="63">
-        <v>31154.04</v>
+        <v>216502.04</v>
       </c>
       <c r="F9" s="64"/>
       <c r="G9" s="64"/>
       <c r="H9" s="65">
         <f t="shared" si="0"/>
-        <v>31154.04</v>
+        <v>216502.04</v>
       </c>
       <c r="I9" s="65">
         <f t="shared" si="1"/>
-        <v>934.62120000000004</v>
+        <v>6495.0612000000001</v>
       </c>
       <c r="J9" s="66">
         <v>0</v>
       </c>
       <c r="K9" s="67">
+        <f>L$2*D9%</f>
+        <v>99801.180580122018</v>
+      </c>
+      <c r="L9" s="68">
+        <f>ROUND(SUM(H9:K9),0) + O9</f>
+        <v>322798.03999999998</v>
+      </c>
+      <c r="M9" s="69">
         <f t="shared" si="2"/>
-        <v>99801.180580122018</v>
-      </c>
-      <c r="L9" s="118">
-        <f>Edesur!M8</f>
-        <v>84612.119880194965</v>
-      </c>
-      <c r="M9" s="68">
+        <v>342166.04</v>
+      </c>
+      <c r="N9" s="70">
         <f t="shared" si="3"/>
-        <v>216502.04</v>
-      </c>
-      <c r="N9" s="69">
+        <v>332482.03999999998</v>
+      </c>
+      <c r="O9" s="39">
         <f t="shared" si="4"/>
-        <v>229492.04</v>
-      </c>
-      <c r="O9" s="70">
-        <f t="shared" si="5"/>
-        <v>222997.04</v>
-      </c>
-      <c r="P9" s="39">
-        <f t="shared" si="6"/>
         <v>0.04</v>
       </c>
-      <c r="R9" s="39"/>
-    </row>
-    <row r="10" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q9" s="39"/>
+    </row>
+    <row r="10" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="57" t="s">
         <v>49</v>
       </c>
@@ -2940,53 +2815,49 @@
         <v>42</v>
       </c>
       <c r="C10" s="58"/>
-      <c r="D10" s="120">
+      <c r="D10" s="117">
         <f>1.02777778+4.9</f>
         <v>5.9277777800000004</v>
       </c>
       <c r="E10" s="63">
-        <v>20456.05</v>
+        <v>165458.04999999999</v>
       </c>
       <c r="F10" s="64"/>
       <c r="G10" s="64"/>
       <c r="H10" s="65">
         <f t="shared" si="0"/>
-        <v>20456.05</v>
+        <v>165458.04999999999</v>
       </c>
       <c r="I10" s="65">
         <f t="shared" si="1"/>
-        <v>613.68149999999991</v>
+        <v>4963.7414999999992</v>
       </c>
       <c r="J10" s="66">
         <v>0</v>
       </c>
       <c r="K10" s="67">
+        <f>L$2*D10%</f>
+        <v>65530.990580122008</v>
+      </c>
+      <c r="L10" s="68">
+        <f>ROUND(SUM(H10:K10),0) + O10</f>
+        <v>235953.05</v>
+      </c>
+      <c r="M10" s="69">
         <f t="shared" si="2"/>
-        <v>65530.990580122008</v>
-      </c>
-      <c r="L10" s="118">
-        <f>Edesur!M9</f>
-        <v>78857.156260194955</v>
-      </c>
-      <c r="M10" s="68">
+        <v>250110.05</v>
+      </c>
+      <c r="N10" s="70">
         <f t="shared" si="3"/>
-        <v>165458.04999999999</v>
-      </c>
-      <c r="N10" s="69">
+        <v>243032.05</v>
+      </c>
+      <c r="O10" s="39">
         <f t="shared" si="4"/>
-        <v>175386.05</v>
-      </c>
-      <c r="O10" s="70">
-        <f t="shared" si="5"/>
-        <v>170422.05</v>
-      </c>
-      <c r="P10" s="39">
-        <f t="shared" si="6"/>
         <v>0.05</v>
       </c>
-      <c r="R10" s="39"/>
-    </row>
-    <row r="11" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q10" s="39"/>
+    </row>
+    <row r="11" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="57" t="s">
         <v>50</v>
       </c>
@@ -2994,20 +2865,21 @@
         <v>43</v>
       </c>
       <c r="C11" s="57"/>
-      <c r="D11" s="120">
+      <c r="D11" s="117">
         <f>1.02777778+3.2</f>
         <v>4.2277777800000003</v>
       </c>
       <c r="E11" s="63">
-        <v>14590.06</v>
-      </c>
-      <c r="F11" s="187">
-        <v>15028.06</v>
+        <v>252613.06</v>
+      </c>
+      <c r="F11" s="184">
+        <f>E11</f>
+        <v>252613.06</v>
       </c>
       <c r="G11" s="64"/>
       <c r="H11" s="65">
         <f t="shared" si="0"/>
-        <v>-438</v>
+        <v>0</v>
       </c>
       <c r="I11" s="65">
         <f t="shared" si="1"/>
@@ -3017,34 +2889,30 @@
         <v>0</v>
       </c>
       <c r="K11" s="67">
+        <f>L$2*D11%</f>
+        <v>46737.660580121999</v>
+      </c>
+      <c r="L11" s="68">
+        <f>ROUND(SUM(H11:K11),0) + O11</f>
+        <v>46738.06</v>
+      </c>
+      <c r="M11" s="69">
         <f t="shared" si="2"/>
-        <v>46737.660580121999</v>
-      </c>
-      <c r="L11" s="118">
-        <f>Edesur!M10</f>
-        <v>196313.01492019495</v>
-      </c>
-      <c r="M11" s="68">
+        <v>49542.06</v>
+      </c>
+      <c r="N11" s="70">
         <f t="shared" si="3"/>
-        <v>242613.06</v>
-      </c>
-      <c r="N11" s="69">
+        <v>48140.06</v>
+      </c>
+      <c r="O11" s="39">
         <f t="shared" si="4"/>
-        <v>257170.06</v>
-      </c>
-      <c r="O11" s="70">
-        <f t="shared" si="5"/>
-        <v>249891.06</v>
-      </c>
-      <c r="P11" s="39">
-        <f t="shared" si="6"/>
         <v>6.0000000000000005E-2</v>
       </c>
-      <c r="Q11" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="12" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="P11" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="57" t="s">
         <v>51</v>
       </c>
@@ -3052,52 +2920,48 @@
         <v>46</v>
       </c>
       <c r="C12" s="57"/>
-      <c r="D12" s="120">
+      <c r="D12" s="117">
         <f>8+1.02777778</f>
         <v>9.027777780000001</v>
       </c>
       <c r="E12" s="63">
-        <v>31154.07</v>
+        <v>211871.07</v>
       </c>
       <c r="F12" s="64"/>
       <c r="G12" s="64"/>
       <c r="H12" s="65">
         <f t="shared" si="0"/>
-        <v>31154.07</v>
+        <v>211871.07</v>
       </c>
       <c r="I12" s="65">
         <f t="shared" si="1"/>
-        <v>934.62209999999993</v>
+        <v>6356.1320999999998</v>
       </c>
       <c r="J12" s="66">
         <v>0</v>
       </c>
       <c r="K12" s="67">
+        <f>L$2*D12%</f>
+        <v>99801.180580122018</v>
+      </c>
+      <c r="L12" s="68">
+        <f>ROUND(SUM(H12:K12),0) + O12</f>
+        <v>318028.07</v>
+      </c>
+      <c r="M12" s="69">
         <f t="shared" si="2"/>
-        <v>99801.180580122018</v>
-      </c>
-      <c r="L12" s="118">
-        <f>Edesur!M11</f>
-        <v>79981.119880194965</v>
-      </c>
-      <c r="M12" s="68">
+        <v>337110.07</v>
+      </c>
+      <c r="N12" s="70">
         <f t="shared" si="3"/>
-        <v>211871.07</v>
-      </c>
-      <c r="N12" s="69">
+        <v>327569.07</v>
+      </c>
+      <c r="O12" s="39">
         <f t="shared" si="4"/>
-        <v>224583.07</v>
-      </c>
-      <c r="O12" s="70">
-        <f t="shared" si="5"/>
-        <v>218227.07</v>
-      </c>
-      <c r="P12" s="39">
-        <f t="shared" si="6"/>
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="57" t="s">
         <v>53</v>
       </c>
@@ -3105,54 +2969,48 @@
         <v>52</v>
       </c>
       <c r="C13" s="58"/>
-      <c r="D13" s="120">
+      <c r="D13" s="117">
         <f>1.02777778+4.9</f>
         <v>5.9277777800000004</v>
       </c>
       <c r="E13" s="63">
-        <v>21070.080000000002</v>
-      </c>
-      <c r="F13" s="187">
-        <v>20456.080000000002</v>
-      </c>
+        <v>286943.08</v>
+      </c>
+      <c r="F13" s="184"/>
       <c r="G13" s="64"/>
       <c r="H13" s="65">
         <f t="shared" si="0"/>
-        <v>614</v>
+        <v>286943.08</v>
       </c>
       <c r="I13" s="65">
         <f t="shared" si="1"/>
-        <v>18.419999999999998</v>
+        <v>8608.2924000000003</v>
       </c>
       <c r="J13" s="66">
         <v>0</v>
       </c>
       <c r="K13" s="67">
+        <f>L$2*D13%</f>
+        <v>65530.990580122008</v>
+      </c>
+      <c r="L13" s="68">
+        <f>ROUND(SUM(H13:K13),0) + O13</f>
+        <v>361082.08</v>
+      </c>
+      <c r="M13" s="69">
         <f t="shared" si="2"/>
-        <v>65530.990580122008</v>
-      </c>
-      <c r="L13" s="118">
-        <f>Edesur!M12</f>
-        <v>220779.15626019496</v>
-      </c>
-      <c r="M13" s="68">
+        <v>382747.08</v>
+      </c>
+      <c r="N13" s="70">
         <f t="shared" si="3"/>
-        <v>286943.08</v>
-      </c>
-      <c r="N13" s="69">
+        <v>371914.08</v>
+      </c>
+      <c r="O13" s="39">
         <f t="shared" si="4"/>
-        <v>304160.08</v>
-      </c>
-      <c r="O13" s="70">
-        <f t="shared" si="5"/>
-        <v>295551.08</v>
-      </c>
-      <c r="P13" s="39">
-        <f t="shared" si="6"/>
         <v>0.08</v>
       </c>
     </row>
-    <row r="14" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="57" t="s">
         <v>54</v>
       </c>
@@ -3160,57 +3018,51 @@
         <v>56</v>
       </c>
       <c r="C14" s="58"/>
-      <c r="D14" s="120">
+      <c r="D14" s="117">
         <f>1.02777778+3.2</f>
         <v>4.2277777800000003</v>
       </c>
       <c r="E14" s="63">
-        <v>14590.09</v>
-      </c>
-      <c r="F14" s="187">
-        <v>15028.09</v>
-      </c>
+        <v>156615.09</v>
+      </c>
+      <c r="F14" s="184"/>
       <c r="G14" s="64"/>
       <c r="H14" s="65">
         <f t="shared" si="0"/>
-        <v>-438</v>
+        <v>156615.09</v>
       </c>
       <c r="I14" s="65">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>4698.4526999999998</v>
       </c>
       <c r="J14" s="66">
         <v>0</v>
       </c>
       <c r="K14" s="67">
+        <f>L$2*D14%</f>
+        <v>46737.660580121999</v>
+      </c>
+      <c r="L14" s="68">
+        <f>ROUND(SUM(H14:K14),0) + O14</f>
+        <v>208051.09</v>
+      </c>
+      <c r="M14" s="69">
         <f t="shared" si="2"/>
-        <v>46737.660580121999</v>
-      </c>
-      <c r="L14" s="118">
-        <f>Edesur!M13</f>
-        <v>110315.01492019495</v>
-      </c>
-      <c r="M14" s="68">
+        <v>220534.09</v>
+      </c>
+      <c r="N14" s="70">
         <f t="shared" si="3"/>
-        <v>156615.09</v>
-      </c>
-      <c r="N14" s="69">
+        <v>214293.09</v>
+      </c>
+      <c r="O14" s="39">
         <f t="shared" si="4"/>
-        <v>166012.09</v>
-      </c>
-      <c r="O14" s="70">
-        <f t="shared" si="5"/>
-        <v>161313.09</v>
-      </c>
-      <c r="P14" s="39">
-        <f t="shared" si="6"/>
         <v>0.09</v>
       </c>
-      <c r="Q14" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="15" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="P14" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="57" t="s">
         <v>55</v>
       </c>
@@ -3218,55 +3070,48 @@
         <v>57</v>
       </c>
       <c r="C15" s="58"/>
-      <c r="D15" s="120">
+      <c r="D15" s="117">
         <f>8+1.02777778</f>
         <v>9.027777780000001</v>
       </c>
       <c r="E15" s="63">
-        <v>32089.1</v>
-      </c>
-      <c r="F15" s="187">
-        <f>E15</f>
-        <v>32089.1</v>
-      </c>
+        <v>471282.1</v>
+      </c>
+      <c r="F15" s="184"/>
       <c r="G15" s="64"/>
       <c r="H15" s="65">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>471282.1</v>
       </c>
       <c r="I15" s="65">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>14138.462999999998</v>
       </c>
       <c r="J15" s="66">
         <v>0</v>
       </c>
       <c r="K15" s="67">
+        <f>L$2*D15%</f>
+        <v>99801.180580122018</v>
+      </c>
+      <c r="L15" s="68">
+        <f>ROUND(SUM(H15:K15),0) + O15</f>
+        <v>585222.1</v>
+      </c>
+      <c r="M15" s="69">
         <f t="shared" si="2"/>
-        <v>99801.180580122018</v>
-      </c>
-      <c r="L15" s="118">
-        <f>Edesur!M14</f>
-        <v>371481.11988019495</v>
-      </c>
-      <c r="M15" s="68">
+        <v>620335.1</v>
+      </c>
+      <c r="N15" s="70">
         <f t="shared" si="3"/>
-        <v>471282.1</v>
-      </c>
-      <c r="N15" s="69">
+        <v>602779.1</v>
+      </c>
+      <c r="O15" s="39">
         <f t="shared" si="4"/>
-        <v>499559.1</v>
-      </c>
-      <c r="O15" s="70">
-        <f t="shared" si="5"/>
-        <v>485420.1</v>
-      </c>
-      <c r="P15" s="39">
-        <f t="shared" si="6"/>
         <v>9.9999999999999992E-2</v>
       </c>
     </row>
-    <row r="16" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="57" t="s">
         <v>61</v>
       </c>
@@ -3274,16 +3119,16 @@
         <v>58</v>
       </c>
       <c r="C16" s="58"/>
-      <c r="D16" s="120">
+      <c r="D16" s="117">
         <f>1.02777778+4.9</f>
         <v>5.9277777800000004</v>
       </c>
       <c r="E16" s="63">
-        <v>21070.11</v>
-      </c>
-      <c r="F16" s="187">
+        <v>184126.11</v>
+      </c>
+      <c r="F16" s="184">
         <f>E16</f>
-        <v>21070.11</v>
+        <v>184126.11</v>
       </c>
       <c r="G16" s="64"/>
       <c r="H16" s="65">
@@ -3298,31 +3143,27 @@
         <v>0</v>
       </c>
       <c r="K16" s="67">
+        <f>L$2*D16%</f>
+        <v>65530.990580122008</v>
+      </c>
+      <c r="L16" s="68">
+        <f>ROUND(SUM(H16:K16),0) + O16</f>
+        <v>65531.11</v>
+      </c>
+      <c r="M16" s="69">
         <f t="shared" si="2"/>
-        <v>65530.990580122008</v>
-      </c>
-      <c r="L16" s="118">
-        <f>Edesur!M15</f>
-        <v>113232.15626019496</v>
-      </c>
-      <c r="M16" s="68">
+        <v>69463.11</v>
+      </c>
+      <c r="N16" s="70">
         <f t="shared" si="3"/>
-        <v>178763.11</v>
-      </c>
-      <c r="N16" s="69">
+        <v>67497.11</v>
+      </c>
+      <c r="O16" s="39">
         <f t="shared" si="4"/>
-        <v>189489.11</v>
-      </c>
-      <c r="O16" s="70">
-        <f t="shared" si="5"/>
-        <v>184126.11</v>
-      </c>
-      <c r="P16" s="39">
-        <f t="shared" si="6"/>
         <v>0.10999999999999999</v>
       </c>
     </row>
-    <row r="17" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="57" t="s">
         <v>62</v>
       </c>
@@ -3330,52 +3171,48 @@
         <v>59</v>
       </c>
       <c r="C17" s="58"/>
-      <c r="D17" s="120">
+      <c r="D17" s="117">
         <f>1.02777778+3.2</f>
         <v>4.2277777800000003</v>
       </c>
       <c r="E17" s="63">
-        <v>14590.12</v>
-      </c>
-      <c r="F17" s="187"/>
+        <v>99546.12</v>
+      </c>
+      <c r="F17" s="184"/>
       <c r="G17" s="64"/>
       <c r="H17" s="65">
         <f t="shared" si="0"/>
-        <v>14590.12</v>
+        <v>99546.12</v>
       </c>
       <c r="I17" s="65">
         <f t="shared" si="1"/>
-        <v>437.70359999999999</v>
+        <v>2986.3835999999997</v>
       </c>
       <c r="J17" s="66">
         <v>0</v>
       </c>
       <c r="K17" s="67">
+        <f>L$2*D17%</f>
+        <v>46737.660580121999</v>
+      </c>
+      <c r="L17" s="68">
+        <f>ROUND(SUM(H17:K17),0) + O17</f>
+        <v>149270.12</v>
+      </c>
+      <c r="M17" s="69">
         <f t="shared" si="2"/>
-        <v>46737.660580121999</v>
-      </c>
-      <c r="L17" s="118">
-        <f>Edesur!M16</f>
-        <v>37781.014920194961</v>
-      </c>
-      <c r="M17" s="68">
+        <v>158226.12</v>
+      </c>
+      <c r="N17" s="70">
         <f t="shared" si="3"/>
-        <v>99546.12</v>
-      </c>
-      <c r="N17" s="69">
+        <v>153748.12</v>
+      </c>
+      <c r="O17" s="39">
         <f t="shared" si="4"/>
-        <v>105519.12</v>
-      </c>
-      <c r="O17" s="70">
-        <f t="shared" si="5"/>
-        <v>102532.12</v>
-      </c>
-      <c r="P17" s="39">
-        <f t="shared" si="6"/>
         <v>0.11999999999999998</v>
       </c>
     </row>
-    <row r="18" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="57" t="s">
         <v>60</v>
       </c>
@@ -3383,74 +3220,69 @@
         <v>46</v>
       </c>
       <c r="C18" s="58"/>
-      <c r="D18" s="120">
+      <c r="D18" s="117">
         <f>1.02777778+5.4+5.7</f>
         <v>12.127777780000001</v>
       </c>
       <c r="E18" s="63">
-        <v>41852.129999999997</v>
-      </c>
-      <c r="F18" s="187">
-        <f>49540-F21</f>
-        <v>41851.839999999997</v>
+        <v>782007.13</v>
+      </c>
+      <c r="F18" s="184">
+        <f>2879.57+4943.5+100000</f>
+        <v>107823.07</v>
       </c>
       <c r="G18" s="64"/>
       <c r="H18" s="65">
         <f t="shared" si="0"/>
-        <v>0.29000000000087311</v>
+        <v>674184.06</v>
       </c>
       <c r="I18" s="65">
         <f t="shared" si="1"/>
-        <v>8.7000000000261937E-3</v>
+        <v>20225.521800000002</v>
       </c>
       <c r="J18" s="66"/>
       <c r="K18" s="67">
-        <f t="shared" si="2"/>
+        <f>L$2*D18%</f>
         <v>134071.37058012199</v>
       </c>
-      <c r="L18" s="118">
-        <f>Edesur!M17</f>
-        <v>647935.08350019495</v>
-      </c>
-      <c r="M18" s="68">
+      <c r="L18" s="68">
+        <f>ROUND(SUM(H18:K18),0) + O18</f>
+        <v>828481.13</v>
+      </c>
+      <c r="M18" s="69"/>
+      <c r="N18" s="70">
         <f t="shared" si="3"/>
-        <v>782007.13</v>
-      </c>
-      <c r="N18" s="69"/>
-      <c r="O18" s="70">
-        <f t="shared" si="5"/>
-        <v>805467.13</v>
-      </c>
-      <c r="P18" s="39">
-        <f t="shared" si="6"/>
+        <v>853335.13</v>
+      </c>
+      <c r="O18" s="39">
+        <f t="shared" si="4"/>
         <v>0.12999999999999998</v>
       </c>
-      <c r="Q18" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="19" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="P18" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="19" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="57"/>
       <c r="B19" s="57"/>
       <c r="C19" s="58"/>
       <c r="D19" s="62"/>
       <c r="E19" s="63"/>
-      <c r="F19" s="187"/>
+      <c r="F19" s="184"/>
       <c r="G19" s="64"/>
       <c r="H19" s="65"/>
       <c r="I19" s="65"/>
       <c r="J19" s="66"/>
       <c r="K19" s="67"/>
-      <c r="L19" s="118"/>
-      <c r="M19" s="68"/>
-      <c r="N19" s="69"/>
-      <c r="O19" s="70"/>
-      <c r="P19" s="39">
-        <f t="shared" si="6"/>
+      <c r="L19" s="68"/>
+      <c r="M19" s="69"/>
+      <c r="N19" s="70"/>
+      <c r="O19" s="39">
+        <f t="shared" si="4"/>
         <v>0.13999999999999999</v>
       </c>
     </row>
-    <row r="20" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="57" t="s">
         <v>63</v>
       </c>
@@ -3458,50 +3290,43 @@
         <v>57</v>
       </c>
       <c r="C20" s="58"/>
-      <c r="D20" s="120">
+      <c r="D20" s="117">
         <f>1.02777778+1.2</f>
         <v>2.2277777800000003</v>
       </c>
       <c r="E20" s="63">
-        <v>7919.15</v>
-      </c>
-      <c r="F20" s="187">
-        <f>E20</f>
-        <v>7919.15</v>
-      </c>
+        <v>43759.15</v>
+      </c>
+      <c r="F20" s="184"/>
       <c r="G20" s="64"/>
       <c r="H20" s="65">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>43759.15</v>
       </c>
       <c r="I20" s="65">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1312.7745</v>
       </c>
       <c r="J20" s="66"/>
       <c r="K20" s="67">
-        <f t="shared" si="2"/>
+        <f>L$2*D20%</f>
         <v>24627.860580122004</v>
       </c>
-      <c r="L20" s="118">
-        <f>Edesur!M19</f>
-        <v>19131.554520194957</v>
-      </c>
-      <c r="M20" s="68">
+      <c r="L20" s="68">
+        <f>ROUND(SUM(H20:K20),0) + O20</f>
+        <v>69700.149999999994</v>
+      </c>
+      <c r="M20" s="69"/>
+      <c r="N20" s="70">
         <f t="shared" si="3"/>
-        <v>43759.15</v>
-      </c>
-      <c r="N20" s="69"/>
-      <c r="O20" s="70">
-        <f t="shared" si="5"/>
-        <v>45072.15</v>
-      </c>
-      <c r="P20" s="39">
-        <f t="shared" si="6"/>
+        <v>71791.149999999994</v>
+      </c>
+      <c r="O20" s="39">
+        <f t="shared" si="4"/>
         <v>0.15</v>
       </c>
     </row>
-    <row r="21" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="57" t="s">
         <v>64</v>
       </c>
@@ -3509,53 +3334,46 @@
         <v>46</v>
       </c>
       <c r="C21" s="58"/>
-      <c r="D21" s="120">
+      <c r="D21" s="117">
         <f>1.02777778+1.2</f>
         <v>2.2277777800000003</v>
       </c>
       <c r="E21" s="63">
-        <v>7688.16</v>
-      </c>
-      <c r="F21" s="187">
-        <f>E21</f>
-        <v>7688.16</v>
-      </c>
+        <v>43759.16</v>
+      </c>
+      <c r="F21" s="184"/>
       <c r="G21" s="64"/>
       <c r="H21" s="65">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>43759.16</v>
       </c>
       <c r="I21" s="65">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1312.7748000000001</v>
       </c>
       <c r="J21" s="66"/>
       <c r="K21" s="67">
-        <f t="shared" si="2"/>
+        <f>L$2*D21%</f>
         <v>24627.860580122004</v>
       </c>
-      <c r="L21" s="118">
-        <f>Edesur!M20</f>
-        <v>19131.554520194957</v>
-      </c>
-      <c r="M21" s="68">
+      <c r="L21" s="68">
+        <f>ROUND(SUM(H21:K21),0) + O21</f>
+        <v>69700.160000000003</v>
+      </c>
+      <c r="M21" s="69"/>
+      <c r="N21" s="70">
         <f t="shared" si="3"/>
-        <v>43759.16</v>
-      </c>
-      <c r="N21" s="69"/>
-      <c r="O21" s="70">
-        <f t="shared" si="5"/>
-        <v>45072.160000000003</v>
-      </c>
-      <c r="P21" s="39">
-        <f t="shared" si="6"/>
+        <v>71791.16</v>
+      </c>
+      <c r="O21" s="39">
+        <f t="shared" si="4"/>
         <v>0.16</v>
       </c>
-      <c r="Q21" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="22" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="P21" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="22" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="57" t="s">
         <v>65</v>
       </c>
@@ -3563,47 +3381,43 @@
         <v>52</v>
       </c>
       <c r="C22" s="58"/>
-      <c r="D22" s="120">
+      <c r="D22" s="117">
         <f>1.02777778+1.2</f>
         <v>2.2277777800000003</v>
       </c>
       <c r="E22" s="63">
-        <v>7688.17</v>
-      </c>
-      <c r="F22" s="187"/>
+        <v>51678.17</v>
+      </c>
+      <c r="F22" s="184"/>
       <c r="G22" s="64"/>
       <c r="H22" s="65">
         <f t="shared" si="0"/>
-        <v>7688.17</v>
+        <v>51678.17</v>
       </c>
       <c r="I22" s="65">
         <f t="shared" si="1"/>
-        <v>230.64509999999999</v>
+        <v>1550.3451</v>
       </c>
       <c r="J22" s="66"/>
       <c r="K22" s="67">
-        <f t="shared" si="2"/>
+        <f>L$2*D22%</f>
         <v>24627.860580122004</v>
       </c>
-      <c r="L22" s="118">
-        <f>Edesur!M21</f>
-        <v>19131.554520194957</v>
-      </c>
-      <c r="M22" s="68">
+      <c r="L22" s="68">
+        <f>ROUND(SUM(H22:K22),0) + O22</f>
+        <v>77856.17</v>
+      </c>
+      <c r="M22" s="69"/>
+      <c r="N22" s="70">
         <f t="shared" si="3"/>
-        <v>51678.17</v>
-      </c>
-      <c r="N22" s="69"/>
-      <c r="O22" s="70">
-        <f t="shared" si="5"/>
-        <v>53228.17</v>
-      </c>
-      <c r="P22" s="39">
-        <f t="shared" si="6"/>
+        <v>80192.17</v>
+      </c>
+      <c r="O22" s="39">
+        <f t="shared" si="4"/>
         <v>0.17</v>
       </c>
     </row>
-    <row r="23" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="57" t="s">
         <v>66</v>
       </c>
@@ -3611,50 +3425,43 @@
         <v>57</v>
       </c>
       <c r="C23" s="58"/>
-      <c r="D23" s="120">
+      <c r="D23" s="117">
         <f>1.02777778+1.2</f>
         <v>2.2277777800000003</v>
       </c>
       <c r="E23" s="63">
-        <v>7910.18</v>
-      </c>
-      <c r="F23" s="187">
-        <f>E23</f>
-        <v>7910.18</v>
-      </c>
+        <v>43759.18</v>
+      </c>
+      <c r="F23" s="184"/>
       <c r="G23" s="64"/>
       <c r="H23" s="65">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>43759.18</v>
       </c>
       <c r="I23" s="65">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1312.7754</v>
       </c>
       <c r="J23" s="66"/>
       <c r="K23" s="67">
-        <f t="shared" si="2"/>
+        <f>L$2*D23%</f>
         <v>24627.860580122004</v>
       </c>
-      <c r="L23" s="118">
-        <f>Edesur!M22</f>
-        <v>19131.554520194957</v>
-      </c>
-      <c r="M23" s="68">
+      <c r="L23" s="68">
+        <f>ROUND(SUM(H23:K23),0) + O23</f>
+        <v>69700.179999999993</v>
+      </c>
+      <c r="M23" s="69"/>
+      <c r="N23" s="70">
         <f t="shared" si="3"/>
-        <v>43759.18</v>
-      </c>
-      <c r="N23" s="69"/>
-      <c r="O23" s="70">
-        <f t="shared" si="5"/>
-        <v>45072.18</v>
-      </c>
-      <c r="P23" s="39">
-        <f t="shared" si="6"/>
+        <v>71791.179999999993</v>
+      </c>
+      <c r="O23" s="39">
+        <f t="shared" si="4"/>
         <v>0.18000000000000002</v>
       </c>
     </row>
-    <row r="24" spans="1:17" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:16" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A24" s="57" t="s">
         <v>67</v>
       </c>
@@ -3662,178 +3469,157 @@
         <v>46</v>
       </c>
       <c r="C24" s="58"/>
-      <c r="D24" s="120">
+      <c r="D24" s="117">
         <f>1.02777778+1.2</f>
         <v>2.2277777800000003</v>
       </c>
       <c r="E24" s="63">
-        <v>7688.19</v>
-      </c>
-      <c r="F24" s="187"/>
+        <v>51678.19</v>
+      </c>
+      <c r="F24" s="184"/>
       <c r="G24" s="64"/>
       <c r="H24" s="65">
         <f t="shared" si="0"/>
-        <v>7688.19</v>
+        <v>51678.19</v>
       </c>
       <c r="I24" s="65">
         <f t="shared" si="1"/>
-        <v>230.64569999999998</v>
+        <v>1550.3457000000001</v>
       </c>
       <c r="J24" s="66">
         <v>0</v>
       </c>
       <c r="K24" s="67">
+        <f>L$2*D24%</f>
+        <v>24627.860580122004</v>
+      </c>
+      <c r="L24" s="68">
+        <f>ROUND(SUM(H24:K24),0) + O24</f>
+        <v>77856.19</v>
+      </c>
+      <c r="M24" s="69">
         <f t="shared" si="2"/>
-        <v>24627.860580122004</v>
-      </c>
-      <c r="L24" s="118">
-        <f>Edesur!M23</f>
-        <v>19131.554520194957</v>
-      </c>
-      <c r="M24" s="68">
+        <v>82528.19</v>
+      </c>
+      <c r="N24" s="70">
         <f t="shared" si="3"/>
-        <v>51678.19</v>
-      </c>
-      <c r="N24" s="69">
+        <v>80192.19</v>
+      </c>
+      <c r="O24" s="39">
         <f t="shared" si="4"/>
-        <v>54779.19</v>
-      </c>
-      <c r="O24" s="70">
-        <f t="shared" si="5"/>
-        <v>53228.19</v>
-      </c>
-      <c r="P24" s="39">
-        <f t="shared" si="6"/>
         <v>0.19000000000000003</v>
       </c>
     </row>
-    <row r="25" spans="1:17" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:16" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A25" s="71"/>
       <c r="B25" s="72"/>
       <c r="C25" s="72"/>
       <c r="D25" s="73">
-        <f t="shared" ref="D25:O25" si="7">SUM(D6:D24)</f>
+        <f t="shared" ref="D25:N25" si="5">SUM(D6:D24)</f>
         <v>100.00000003999999</v>
       </c>
       <c r="E25" s="47">
-        <f t="shared" si="7"/>
-        <v>349082.76</v>
+        <f t="shared" si="5"/>
+        <v>3763785.7600000002</v>
       </c>
       <c r="F25" s="55">
-        <f t="shared" si="7"/>
-        <v>236613.83</v>
+        <f t="shared" si="5"/>
+        <v>986668.29</v>
       </c>
       <c r="G25" s="47">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="H25" s="55">
-        <f t="shared" si="7"/>
-        <v>112468.93000000001</v>
+        <f t="shared" si="5"/>
+        <v>2777117.4700000007</v>
       </c>
       <c r="I25" s="55">
-        <f t="shared" si="7"/>
-        <v>3400.3478999999998</v>
+        <f t="shared" si="5"/>
+        <v>83313.52410000001</v>
       </c>
       <c r="J25" s="55">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="K25" s="104">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="K25" s="102">
+        <f t="shared" si="5"/>
         <v>1105490.0004421964</v>
       </c>
-      <c r="L25" s="55">
-        <f t="shared" si="7"/>
-        <v>2521214.0203435086</v>
+      <c r="L25" s="74">
+        <f t="shared" si="5"/>
+        <v>3965922.7600000002</v>
       </c>
       <c r="M25" s="74">
-        <f t="shared" si="7"/>
-        <v>3742573.7600000002</v>
+        <f t="shared" si="5"/>
+        <v>3021513.97</v>
       </c>
       <c r="N25" s="74">
-        <f t="shared" si="7"/>
-        <v>2944269.97</v>
-      </c>
-      <c r="O25" s="74">
-        <f t="shared" si="7"/>
-        <v>3854848.7600000002</v>
-      </c>
-    </row>
-    <row r="26" spans="1:17" x14ac:dyDescent="0.25">
+        <f t="shared" si="5"/>
+        <v>4084901.7600000002</v>
+      </c>
+    </row>
+    <row r="26" spans="1:16" x14ac:dyDescent="0.3">
       <c r="B26" s="46"/>
       <c r="C26" s="46"/>
-      <c r="D26" s="119"/>
-    </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="B27" s="194" t="s">
+      <c r="D26" s="116"/>
+    </row>
+    <row r="27" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="B27" s="191" t="s">
         <v>85</v>
       </c>
-      <c r="C27" s="194"/>
-      <c r="D27" s="194"/>
-      <c r="E27" s="194"/>
-      <c r="F27" s="194"/>
-      <c r="G27" s="194"/>
-      <c r="H27" s="194"/>
-      <c r="I27" s="194"/>
-      <c r="J27" s="194"/>
-      <c r="K27" s="194"/>
-      <c r="L27" s="194"/>
-      <c r="M27" s="194"/>
-    </row>
-    <row r="28" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="B28" s="194"/>
-      <c r="C28" s="194"/>
-      <c r="D28" s="194"/>
-      <c r="E28" s="194"/>
-      <c r="F28" s="194"/>
-      <c r="G28" s="194"/>
-      <c r="H28" s="194"/>
-      <c r="I28" s="194"/>
-      <c r="J28" s="194"/>
-      <c r="K28" s="194"/>
-      <c r="L28" s="194"/>
-      <c r="M28" s="194"/>
-    </row>
-    <row r="29" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="B29" s="194"/>
-      <c r="C29" s="194"/>
-      <c r="D29" s="194"/>
-      <c r="E29" s="194"/>
-      <c r="F29" s="194"/>
-      <c r="G29" s="194"/>
-      <c r="H29" s="194"/>
-      <c r="I29" s="194"/>
-      <c r="J29" s="194"/>
-      <c r="K29" s="194"/>
-      <c r="L29" s="194"/>
-      <c r="M29" s="194"/>
-    </row>
-    <row r="30" spans="1:17" ht="72" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B30" s="194"/>
-      <c r="C30" s="194"/>
-      <c r="D30" s="194"/>
-      <c r="E30" s="194"/>
-      <c r="F30" s="194"/>
-      <c r="G30" s="194"/>
-      <c r="H30" s="194"/>
-      <c r="I30" s="194"/>
-      <c r="J30" s="194"/>
-      <c r="K30" s="194"/>
-      <c r="L30" s="194"/>
-      <c r="M30" s="194"/>
+      <c r="C27" s="191"/>
+      <c r="D27" s="191"/>
+      <c r="E27" s="191"/>
+      <c r="F27" s="191"/>
+      <c r="G27" s="191"/>
+      <c r="H27" s="191"/>
+      <c r="I27" s="191"/>
+      <c r="J27" s="191"/>
+      <c r="K27" s="191"/>
+      <c r="L27" s="191"/>
+    </row>
+    <row r="28" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="B28" s="191"/>
+      <c r="C28" s="191"/>
+      <c r="D28" s="191"/>
+      <c r="E28" s="191"/>
+      <c r="F28" s="191"/>
+      <c r="G28" s="191"/>
+      <c r="H28" s="191"/>
+      <c r="I28" s="191"/>
+      <c r="J28" s="191"/>
+      <c r="K28" s="191"/>
+      <c r="L28" s="191"/>
+    </row>
+    <row r="29" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="B29" s="191"/>
+      <c r="C29" s="191"/>
+      <c r="D29" s="191"/>
+      <c r="E29" s="191"/>
+      <c r="F29" s="191"/>
+      <c r="G29" s="191"/>
+      <c r="H29" s="191"/>
+      <c r="I29" s="191"/>
+      <c r="J29" s="191"/>
+      <c r="K29" s="191"/>
+      <c r="L29" s="191"/>
+    </row>
+    <row r="30" spans="1:16" ht="72" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B30" s="191"/>
+      <c r="C30" s="191"/>
+      <c r="D30" s="191"/>
+      <c r="E30" s="191"/>
+      <c r="F30" s="191"/>
+      <c r="G30" s="191"/>
+      <c r="H30" s="191"/>
+      <c r="I30" s="191"/>
+      <c r="J30" s="191"/>
+      <c r="K30" s="191"/>
+      <c r="L30" s="191"/>
     </row>
   </sheetData>
-  <mergeCells count="16">
-    <mergeCell ref="B2:H3"/>
-    <mergeCell ref="O4:O5"/>
-    <mergeCell ref="B27:M30"/>
-    <mergeCell ref="C4:C5"/>
-    <mergeCell ref="G4:G5"/>
-    <mergeCell ref="N4:N5"/>
-    <mergeCell ref="J4:J5"/>
-    <mergeCell ref="K4:K5"/>
-    <mergeCell ref="L4:L5"/>
+  <mergeCells count="15">
     <mergeCell ref="A4:A5"/>
     <mergeCell ref="B4:B5"/>
     <mergeCell ref="D4:D5"/>
@@ -3841,6 +3627,14 @@
     <mergeCell ref="E4:E5"/>
     <mergeCell ref="F4:F5"/>
     <mergeCell ref="H4:H5"/>
+    <mergeCell ref="B2:H3"/>
+    <mergeCell ref="N4:N5"/>
+    <mergeCell ref="B27:L30"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="G4:G5"/>
+    <mergeCell ref="M4:M5"/>
+    <mergeCell ref="J4:J5"/>
+    <mergeCell ref="K4:K5"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>
@@ -3850,1108 +3644,1107 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{642D1833-D35F-45AC-9D7A-9C6C07C828FD}">
   <dimension ref="A1:Q32"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="5" hidden="1" customWidth="1"/>
-    <col min="2" max="2" width="8.28515625" hidden="1" customWidth="1"/>
-    <col min="3" max="3" width="7.5703125" customWidth="1"/>
-    <col min="4" max="4" width="23.7109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.33203125" hidden="1" customWidth="1"/>
+    <col min="3" max="3" width="7.5546875" customWidth="1"/>
+    <col min="4" max="4" width="23.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.5546875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="12" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8.28515625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="7.28515625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.33203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="7.33203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.44140625" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="8" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="11.28515625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="8.7109375" customWidth="1"/>
-    <col min="13" max="13" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.33203125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8.6640625" customWidth="1"/>
+    <col min="13" max="13" width="11.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="216" t="s">
+    <row r="1" spans="1:17" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="211" t="s">
         <v>69</v>
       </c>
-      <c r="B1" s="217"/>
-      <c r="C1" s="217"/>
-      <c r="D1" s="217"/>
-      <c r="E1" s="217"/>
-      <c r="F1" s="217"/>
-      <c r="G1" s="217"/>
-      <c r="H1" s="217"/>
-      <c r="I1" s="217"/>
-      <c r="J1" s="217"/>
-      <c r="K1" s="217"/>
-      <c r="L1" s="217"/>
-      <c r="M1" s="218"/>
-    </row>
-    <row r="2" spans="1:17" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="126"/>
-      <c r="B2" s="126" t="s">
+      <c r="B1" s="212"/>
+      <c r="C1" s="212"/>
+      <c r="D1" s="212"/>
+      <c r="E1" s="212"/>
+      <c r="F1" s="212"/>
+      <c r="G1" s="212"/>
+      <c r="H1" s="212"/>
+      <c r="I1" s="212"/>
+      <c r="J1" s="212"/>
+      <c r="K1" s="212"/>
+      <c r="L1" s="212"/>
+      <c r="M1" s="213"/>
+    </row>
+    <row r="2" spans="1:17" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="123"/>
+      <c r="B2" s="123" t="s">
         <v>69</v>
       </c>
-      <c r="C2" s="127"/>
-      <c r="D2" s="184">
+      <c r="C2" s="124"/>
+      <c r="D2" s="181">
         <v>2521214.02</v>
       </c>
-      <c r="E2" s="121"/>
-      <c r="F2" s="121"/>
-      <c r="G2" s="121"/>
-      <c r="H2" s="122"/>
-      <c r="I2" s="121"/>
-      <c r="J2" s="121"/>
-      <c r="K2" s="121"/>
-      <c r="L2" s="121"/>
-      <c r="M2" s="121"/>
-      <c r="N2" s="124"/>
-    </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A3" s="126"/>
-      <c r="B3" s="125" t="s">
+      <c r="E2" s="118"/>
+      <c r="F2" s="118"/>
+      <c r="G2" s="118"/>
+      <c r="H2" s="119"/>
+      <c r="I2" s="118"/>
+      <c r="J2" s="118"/>
+      <c r="K2" s="118"/>
+      <c r="L2" s="118"/>
+      <c r="M2" s="118"/>
+      <c r="N2" s="121"/>
+    </row>
+    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A3" s="123"/>
+      <c r="B3" s="122" t="s">
         <v>69</v>
       </c>
-      <c r="C3" s="221">
-        <f>D2</f>
-        <v>2521214.02</v>
-      </c>
-      <c r="D3" s="221"/>
-      <c r="E3" s="128"/>
-      <c r="F3" s="128"/>
-      <c r="G3" s="128"/>
-      <c r="H3" s="129"/>
-      <c r="I3" s="123"/>
-      <c r="J3" s="130"/>
-      <c r="K3" s="219">
+      <c r="C3" s="216">
+        <v>0</v>
+      </c>
+      <c r="D3" s="216"/>
+      <c r="E3" s="125"/>
+      <c r="F3" s="125"/>
+      <c r="G3" s="125"/>
+      <c r="H3" s="126"/>
+      <c r="I3" s="120"/>
+      <c r="J3" s="127"/>
+      <c r="K3" s="214">
         <f>D2-I24</f>
         <v>858773.02</v>
       </c>
-      <c r="L3" s="219"/>
-      <c r="M3" s="131"/>
-      <c r="N3" s="124"/>
-    </row>
-    <row r="4" spans="1:17" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="132" t="s">
+      <c r="L3" s="214"/>
+      <c r="M3" s="128"/>
+      <c r="N3" s="121"/>
+    </row>
+    <row r="4" spans="1:17" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="129" t="s">
         <v>70</v>
       </c>
-      <c r="B4" s="132" t="s">
+      <c r="B4" s="129" t="s">
         <v>70</v>
       </c>
-      <c r="C4" s="133" t="s">
+      <c r="C4" s="130" t="s">
         <v>71</v>
       </c>
-      <c r="D4" s="134" t="s">
+      <c r="D4" s="131" t="s">
         <v>72</v>
       </c>
-      <c r="E4" s="134" t="s">
+      <c r="E4" s="131" t="s">
         <v>73</v>
       </c>
-      <c r="F4" s="135" t="s">
+      <c r="F4" s="132" t="s">
         <v>74</v>
       </c>
-      <c r="G4" s="135" t="s">
+      <c r="G4" s="132" t="s">
         <v>75</v>
       </c>
-      <c r="H4" s="136" t="s">
+      <c r="H4" s="133" t="s">
         <v>76</v>
       </c>
-      <c r="I4" s="137" t="s">
+      <c r="I4" s="134" t="s">
         <v>69</v>
       </c>
-      <c r="J4" s="174" t="s">
+      <c r="J4" s="171" t="s">
         <v>77</v>
       </c>
-      <c r="K4" s="174" t="s">
+      <c r="K4" s="171" t="s">
         <v>77</v>
       </c>
-      <c r="L4" s="138" t="s">
+      <c r="L4" s="135" t="s">
         <v>76</v>
       </c>
-      <c r="M4" s="135" t="s">
+      <c r="M4" s="132" t="s">
         <v>78</v>
       </c>
-      <c r="N4" s="124"/>
-    </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A5" s="139">
+      <c r="N4" s="121"/>
+    </row>
+    <row r="5" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A5" s="136">
         <v>1</v>
       </c>
-      <c r="B5" s="140">
+      <c r="B5" s="137">
         <v>1</v>
       </c>
-      <c r="C5" s="141" t="str">
+      <c r="C5" s="138" t="str">
         <f>PRORRATEO!A6</f>
         <v>1A</v>
       </c>
-      <c r="D5" s="142" t="str">
+      <c r="D5" s="139" t="str">
         <f>PRORRATEO!B6</f>
         <v>Chida Gustavo Daniel</v>
       </c>
-      <c r="E5" s="143">
+      <c r="E5" s="140">
         <v>9.027777780000001</v>
       </c>
-      <c r="F5" s="144">
-        <v>0</v>
-      </c>
-      <c r="G5" s="144">
+      <c r="F5" s="141">
+        <v>0</v>
+      </c>
+      <c r="G5" s="141">
         <v>752.3</v>
       </c>
-      <c r="H5" s="145">
+      <c r="H5" s="142">
         <f>G5-F5</f>
         <v>752.3</v>
       </c>
-      <c r="I5" s="146">
+      <c r="I5" s="143">
         <f>L5*110</f>
         <v>82753</v>
       </c>
-      <c r="J5" s="146">
+      <c r="J5" s="143">
         <f>J3*E5%</f>
         <v>0</v>
       </c>
-      <c r="K5" s="176">
+      <c r="K5" s="173">
         <f>K$3*E5/Q$7</f>
         <v>77528.119880194965</v>
       </c>
-      <c r="L5" s="147">
+      <c r="L5" s="144">
         <f t="shared" ref="L5:L21" si="0">G5-F5</f>
         <v>752.3</v>
       </c>
-      <c r="M5" s="145">
+      <c r="M5" s="142">
         <f>I5+K5</f>
         <v>160281.11988019495</v>
       </c>
-      <c r="N5" s="124"/>
-    </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A6" s="149">
+      <c r="N5" s="121"/>
+    </row>
+    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A6" s="146">
         <v>2</v>
       </c>
-      <c r="B6" s="150">
+      <c r="B6" s="147">
         <v>2</v>
       </c>
-      <c r="C6" s="141" t="str">
+      <c r="C6" s="138" t="str">
         <f>PRORRATEO!A7</f>
         <v>1B</v>
       </c>
-      <c r="D6" s="142" t="str">
+      <c r="D6" s="139" t="str">
         <f>PRORRATEO!B7</f>
         <v>D' Andrea Patricia Daniela</v>
       </c>
-      <c r="E6" s="143">
+      <c r="E6" s="140">
         <v>5.9277777800000004</v>
       </c>
-      <c r="F6" s="144">
-        <v>0</v>
-      </c>
-      <c r="G6" s="144">
+      <c r="F6" s="141">
+        <v>0</v>
+      </c>
+      <c r="G6" s="141">
         <v>1135.0999999999999</v>
       </c>
-      <c r="H6" s="145">
+      <c r="H6" s="142">
         <f t="shared" ref="H6:H22" si="1">G6-F6</f>
         <v>1135.0999999999999</v>
       </c>
-      <c r="I6" s="146">
+      <c r="I6" s="143">
         <f t="shared" ref="I6:I17" si="2">L6*110</f>
         <v>124860.99999999999</v>
       </c>
-      <c r="J6" s="146">
+      <c r="J6" s="143">
         <f>J3*E6%</f>
         <v>0</v>
       </c>
-      <c r="K6" s="176">
+      <c r="K6" s="173">
         <f t="shared" ref="K6:K23" si="3">K$3*E6/Q$7</f>
         <v>50906.156260194963</v>
       </c>
-      <c r="L6" s="147">
+      <c r="L6" s="144">
         <f t="shared" si="0"/>
         <v>1135.0999999999999</v>
       </c>
-      <c r="M6" s="145">
+      <c r="M6" s="142">
         <f t="shared" ref="M6:M20" si="4">I6+K6</f>
         <v>175767.15626019496</v>
       </c>
-      <c r="N6" s="124"/>
-    </row>
-    <row r="7" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="139">
+      <c r="N6" s="121"/>
+    </row>
+    <row r="7" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="136">
         <v>3</v>
       </c>
-      <c r="B7" s="150">
+      <c r="B7" s="147">
         <v>3</v>
       </c>
-      <c r="C7" s="141" t="str">
+      <c r="C7" s="138" t="str">
         <f>PRORRATEO!A8</f>
         <v>1C</v>
       </c>
-      <c r="D7" s="142" t="str">
+      <c r="D7" s="139" t="str">
         <f>PRORRATEO!B8</f>
         <v>Arroyo Aldana</v>
       </c>
-      <c r="E7" s="143">
+      <c r="E7" s="140">
         <v>4.2277777800000003</v>
       </c>
-      <c r="F7" s="144">
-        <v>0</v>
-      </c>
-      <c r="G7" s="144">
+      <c r="F7" s="141">
+        <v>0</v>
+      </c>
+      <c r="G7" s="141">
         <v>1017.4</v>
       </c>
-      <c r="H7" s="145">
+      <c r="H7" s="142">
         <f t="shared" si="1"/>
         <v>1017.4</v>
       </c>
-      <c r="I7" s="146">
+      <c r="I7" s="143">
         <f t="shared" si="2"/>
         <v>111914</v>
       </c>
-      <c r="J7" s="146">
+      <c r="J7" s="143">
         <f>J3*E7%</f>
         <v>0</v>
       </c>
-      <c r="K7" s="176">
+      <c r="K7" s="173">
         <f t="shared" si="3"/>
         <v>36307.014920194961</v>
       </c>
-      <c r="L7" s="147">
+      <c r="L7" s="144">
         <f t="shared" si="0"/>
         <v>1017.4</v>
       </c>
-      <c r="M7" s="145">
+      <c r="M7" s="142">
         <f t="shared" si="4"/>
         <v>148221.01492019495</v>
       </c>
-      <c r="N7" s="124"/>
+      <c r="N7" s="121"/>
       <c r="Q7">
         <v>100</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A8" s="139">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A8" s="136">
         <v>4</v>
       </c>
-      <c r="B8" s="150" t="s">
+      <c r="B8" s="147" t="s">
         <v>79</v>
       </c>
-      <c r="C8" s="141" t="str">
+      <c r="C8" s="138" t="str">
         <f>PRORRATEO!A9</f>
         <v>2A</v>
       </c>
-      <c r="D8" s="142" t="str">
+      <c r="D8" s="139" t="str">
         <f>PRORRATEO!B9</f>
         <v>Stagno Jorge Adrian</v>
       </c>
-      <c r="E8" s="151">
+      <c r="E8" s="148">
         <v>9.027777780000001</v>
       </c>
-      <c r="F8" s="144">
-        <v>0</v>
-      </c>
-      <c r="G8" s="144">
+      <c r="F8" s="141">
+        <v>0</v>
+      </c>
+      <c r="G8" s="141">
         <v>64.400000000000006</v>
       </c>
-      <c r="H8" s="145">
+      <c r="H8" s="142">
         <f t="shared" si="1"/>
         <v>64.400000000000006</v>
       </c>
-      <c r="I8" s="146">
+      <c r="I8" s="143">
         <f t="shared" si="2"/>
         <v>7084.0000000000009</v>
       </c>
-      <c r="J8" s="177">
+      <c r="J8" s="174">
         <f>J3*E8%</f>
         <v>0</v>
       </c>
-      <c r="K8" s="176">
+      <c r="K8" s="173">
         <f t="shared" si="3"/>
         <v>77528.119880194965</v>
       </c>
-      <c r="L8" s="152">
+      <c r="L8" s="149">
         <f t="shared" si="0"/>
         <v>64.400000000000006</v>
       </c>
-      <c r="M8" s="145">
+      <c r="M8" s="142">
         <f t="shared" si="4"/>
         <v>84612.119880194965</v>
       </c>
-      <c r="N8" s="124"/>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A9" s="139">
+      <c r="N8" s="121"/>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A9" s="136">
         <v>6</v>
       </c>
-      <c r="B9" s="150">
+      <c r="B9" s="147">
         <v>6</v>
       </c>
-      <c r="C9" s="141" t="str">
+      <c r="C9" s="138" t="str">
         <f>PRORRATEO!A10</f>
         <v>2B</v>
       </c>
-      <c r="D9" s="142" t="str">
+      <c r="D9" s="139" t="str">
         <f>PRORRATEO!B10</f>
         <v>Stagno Jorge Adrian</v>
       </c>
-      <c r="E9" s="143">
+      <c r="E9" s="140">
         <v>5.9277777800000004</v>
       </c>
-      <c r="F9" s="144">
-        <v>0</v>
-      </c>
-      <c r="G9" s="144">
+      <c r="F9" s="141">
+        <v>0</v>
+      </c>
+      <c r="G9" s="141">
         <v>254.1</v>
       </c>
-      <c r="H9" s="145">
+      <c r="H9" s="142">
         <f t="shared" si="1"/>
         <v>254.1</v>
       </c>
-      <c r="I9" s="146">
+      <c r="I9" s="143">
         <f t="shared" si="2"/>
         <v>27951</v>
       </c>
-      <c r="J9" s="146">
+      <c r="J9" s="143">
         <f>J3*E9%</f>
         <v>0</v>
       </c>
-      <c r="K9" s="176">
+      <c r="K9" s="173">
         <f t="shared" si="3"/>
         <v>50906.156260194963</v>
       </c>
-      <c r="L9" s="147">
+      <c r="L9" s="144">
         <f t="shared" si="0"/>
         <v>254.1</v>
       </c>
-      <c r="M9" s="145">
+      <c r="M9" s="142">
         <f t="shared" si="4"/>
         <v>78857.156260194955</v>
       </c>
-      <c r="N9" s="124"/>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A10" s="139">
+      <c r="N9" s="121"/>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A10" s="136">
         <v>7</v>
       </c>
-      <c r="B10" s="150">
+      <c r="B10" s="147">
         <v>7</v>
       </c>
-      <c r="C10" s="141" t="str">
+      <c r="C10" s="138" t="str">
         <f>PRORRATEO!A11</f>
         <v>2C</v>
       </c>
-      <c r="D10" s="142" t="str">
+      <c r="D10" s="139" t="str">
         <f>PRORRATEO!B11</f>
         <v>Beneyte Lenorado Damian</v>
       </c>
-      <c r="E10" s="143">
+      <c r="E10" s="140">
         <v>4.2277777800000003</v>
       </c>
-      <c r="F10" s="144">
-        <v>0</v>
-      </c>
-      <c r="G10" s="144">
+      <c r="F10" s="141">
+        <v>0</v>
+      </c>
+      <c r="G10" s="141">
         <v>1454.6</v>
       </c>
-      <c r="H10" s="145">
+      <c r="H10" s="142">
         <f t="shared" si="1"/>
         <v>1454.6</v>
       </c>
-      <c r="I10" s="146">
+      <c r="I10" s="143">
         <f t="shared" si="2"/>
         <v>160006</v>
       </c>
-      <c r="J10" s="146">
+      <c r="J10" s="143">
         <f>J3*E10%</f>
         <v>0</v>
       </c>
-      <c r="K10" s="176">
+      <c r="K10" s="173">
         <f t="shared" si="3"/>
         <v>36307.014920194961</v>
       </c>
-      <c r="L10" s="147">
+      <c r="L10" s="144">
         <f t="shared" si="0"/>
         <v>1454.6</v>
       </c>
-      <c r="M10" s="145">
+      <c r="M10" s="142">
         <f t="shared" si="4"/>
         <v>196313.01492019495</v>
       </c>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A11" s="139">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A11" s="136">
         <v>8</v>
       </c>
-      <c r="B11" s="150">
+      <c r="B11" s="147">
         <v>8</v>
       </c>
-      <c r="C11" s="141" t="str">
+      <c r="C11" s="138" t="str">
         <f>PRORRATEO!A12</f>
         <v>3A</v>
       </c>
-      <c r="D11" s="142" t="str">
+      <c r="D11" s="139" t="str">
         <f>PRORRATEO!B12</f>
         <v>Sr Propietario</v>
       </c>
-      <c r="E11" s="143">
+      <c r="E11" s="140">
         <v>9.027777780000001</v>
       </c>
-      <c r="F11" s="144">
-        <v>0</v>
-      </c>
-      <c r="G11" s="144">
+      <c r="F11" s="141">
+        <v>0</v>
+      </c>
+      <c r="G11" s="141">
         <v>22.3</v>
       </c>
-      <c r="H11" s="145">
+      <c r="H11" s="142">
         <f t="shared" si="1"/>
         <v>22.3</v>
       </c>
-      <c r="I11" s="146">
+      <c r="I11" s="143">
         <f t="shared" si="2"/>
         <v>2453</v>
       </c>
-      <c r="J11" s="146">
+      <c r="J11" s="143">
         <f>J3*E11%</f>
         <v>0</v>
       </c>
-      <c r="K11" s="176">
+      <c r="K11" s="173">
         <f t="shared" si="3"/>
         <v>77528.119880194965</v>
       </c>
-      <c r="L11" s="147">
+      <c r="L11" s="144">
         <f t="shared" si="0"/>
         <v>22.3</v>
       </c>
-      <c r="M11" s="145">
+      <c r="M11" s="142">
         <f t="shared" si="4"/>
         <v>79981.119880194965</v>
       </c>
     </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A12" s="139">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A12" s="136">
         <v>9</v>
       </c>
-      <c r="B12" s="150">
+      <c r="B12" s="147">
         <v>9</v>
       </c>
-      <c r="C12" s="141" t="str">
+      <c r="C12" s="138" t="str">
         <f>PRORRATEO!A13</f>
         <v>3B</v>
       </c>
-      <c r="D12" s="142" t="str">
+      <c r="D12" s="139" t="str">
         <f>PRORRATEO!B13</f>
         <v>Torres Lilliana Beatriz</v>
       </c>
-      <c r="E12" s="143">
+      <c r="E12" s="140">
         <v>5.9277777800000004</v>
       </c>
-      <c r="F12" s="144">
-        <v>0</v>
-      </c>
-      <c r="G12" s="144">
+      <c r="F12" s="141">
+        <v>0</v>
+      </c>
+      <c r="G12" s="141">
         <v>1544.3</v>
       </c>
-      <c r="H12" s="145">
+      <c r="H12" s="142">
         <f t="shared" si="1"/>
         <v>1544.3</v>
       </c>
-      <c r="I12" s="146">
+      <c r="I12" s="143">
         <f t="shared" si="2"/>
         <v>169873</v>
       </c>
-      <c r="J12" s="146">
+      <c r="J12" s="143">
         <f>J3*E12%</f>
         <v>0</v>
       </c>
-      <c r="K12" s="176">
+      <c r="K12" s="173">
         <f t="shared" si="3"/>
         <v>50906.156260194963</v>
       </c>
-      <c r="L12" s="147">
+      <c r="L12" s="144">
         <f t="shared" si="0"/>
         <v>1544.3</v>
       </c>
-      <c r="M12" s="145">
+      <c r="M12" s="142">
         <f t="shared" si="4"/>
         <v>220779.15626019496</v>
       </c>
     </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A13" s="139">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A13" s="136">
         <v>10</v>
       </c>
-      <c r="B13" s="150">
+      <c r="B13" s="147">
         <v>10</v>
       </c>
-      <c r="C13" s="141" t="str">
+      <c r="C13" s="138" t="str">
         <f>PRORRATEO!A14</f>
         <v>3C</v>
       </c>
-      <c r="D13" s="142" t="str">
+      <c r="D13" s="139" t="str">
         <f>PRORRATEO!B14</f>
         <v>Arostegui Hector/Herrera Monica</v>
       </c>
-      <c r="E13" s="143">
+      <c r="E13" s="140">
         <v>4.2277777800000003</v>
       </c>
-      <c r="F13" s="144">
-        <v>0</v>
-      </c>
-      <c r="G13" s="144">
+      <c r="F13" s="141">
+        <v>0</v>
+      </c>
+      <c r="G13" s="141">
         <v>672.8</v>
       </c>
-      <c r="H13" s="145">
+      <c r="H13" s="142">
         <f t="shared" si="1"/>
         <v>672.8</v>
       </c>
-      <c r="I13" s="146">
+      <c r="I13" s="143">
         <f t="shared" si="2"/>
         <v>74008</v>
       </c>
-      <c r="J13" s="146">
+      <c r="J13" s="143">
         <f>J3*E13%</f>
         <v>0</v>
       </c>
-      <c r="K13" s="176">
+      <c r="K13" s="173">
         <f t="shared" si="3"/>
         <v>36307.014920194961</v>
       </c>
-      <c r="L13" s="147">
+      <c r="L13" s="144">
         <f t="shared" si="0"/>
         <v>672.8</v>
       </c>
-      <c r="M13" s="145">
+      <c r="M13" s="142">
         <f t="shared" si="4"/>
         <v>110315.01492019495</v>
       </c>
     </row>
-    <row r="14" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="139">
+    <row r="14" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="136">
         <v>11</v>
       </c>
-      <c r="B14" s="150">
+      <c r="B14" s="147">
         <v>11</v>
       </c>
-      <c r="C14" s="141" t="str">
+      <c r="C14" s="138" t="str">
         <f>PRORRATEO!A15</f>
         <v>4A</v>
       </c>
-      <c r="D14" s="142" t="str">
+      <c r="D14" s="139" t="str">
         <f>PRORRATEO!B15</f>
         <v>Frosio Diego Martin</v>
       </c>
-      <c r="E14" s="143">
+      <c r="E14" s="140">
         <v>9.027777780000001</v>
       </c>
-      <c r="F14" s="144">
-        <v>0</v>
-      </c>
-      <c r="G14" s="144">
+      <c r="F14" s="141">
+        <v>0</v>
+      </c>
+      <c r="G14" s="141">
         <v>2672.3</v>
       </c>
-      <c r="H14" s="145">
+      <c r="H14" s="142">
         <f t="shared" si="1"/>
         <v>2672.3</v>
       </c>
-      <c r="I14" s="146">
+      <c r="I14" s="143">
         <f t="shared" si="2"/>
         <v>293953</v>
       </c>
-      <c r="J14" s="146">
+      <c r="J14" s="143">
         <f>J3*E14%</f>
         <v>0</v>
       </c>
-      <c r="K14" s="176">
+      <c r="K14" s="173">
         <f t="shared" si="3"/>
         <v>77528.119880194965</v>
       </c>
-      <c r="L14" s="147">
+      <c r="L14" s="144">
         <f t="shared" si="0"/>
         <v>2672.3</v>
       </c>
-      <c r="M14" s="145">
+      <c r="M14" s="142">
         <f t="shared" si="4"/>
         <v>371481.11988019495</v>
       </c>
     </row>
-    <row r="15" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="139">
+    <row r="15" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="136">
         <v>12</v>
       </c>
-      <c r="B15" s="150">
+      <c r="B15" s="147">
         <v>12</v>
       </c>
-      <c r="C15" s="141" t="str">
+      <c r="C15" s="138" t="str">
         <f>PRORRATEO!A16</f>
         <v>4B</v>
       </c>
-      <c r="D15" s="142" t="str">
+      <c r="D15" s="139" t="str">
         <f>PRORRATEO!B16</f>
         <v>Actis Sofia Magali</v>
       </c>
-      <c r="E15" s="143">
+      <c r="E15" s="140">
         <v>5.9277777800000004</v>
       </c>
-      <c r="F15" s="144">
-        <v>0</v>
-      </c>
-      <c r="G15" s="144">
+      <c r="F15" s="141">
+        <v>0</v>
+      </c>
+      <c r="G15" s="141">
         <v>566.6</v>
       </c>
-      <c r="H15" s="145">
+      <c r="H15" s="142">
         <f t="shared" si="1"/>
         <v>566.6</v>
       </c>
-      <c r="I15" s="146">
+      <c r="I15" s="143">
         <f t="shared" si="2"/>
         <v>62326</v>
       </c>
-      <c r="J15" s="146">
+      <c r="J15" s="143">
         <f>J3*E15%</f>
         <v>0</v>
       </c>
-      <c r="K15" s="176">
+      <c r="K15" s="173">
         <f>K$3*E15/Q$7</f>
         <v>50906.156260194963</v>
       </c>
-      <c r="L15" s="147">
+      <c r="L15" s="144">
         <f t="shared" si="0"/>
         <v>566.6</v>
       </c>
-      <c r="M15" s="145">
+      <c r="M15" s="142">
         <f t="shared" si="4"/>
         <v>113232.15626019496</v>
       </c>
     </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A16" s="139">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A16" s="136">
         <v>13</v>
       </c>
-      <c r="B16" s="150">
+      <c r="B16" s="147">
         <v>13</v>
       </c>
-      <c r="C16" s="141" t="str">
+      <c r="C16" s="138" t="str">
         <f>PRORRATEO!A17</f>
         <v>4C</v>
       </c>
-      <c r="D16" s="142" t="str">
+      <c r="D16" s="139" t="str">
         <f>PRORRATEO!B17</f>
         <v>Alanis Hebert</v>
       </c>
-      <c r="E16" s="143">
+      <c r="E16" s="140">
         <v>4.2277777800000003</v>
       </c>
-      <c r="F16" s="144">
-        <v>0</v>
-      </c>
-      <c r="G16" s="144">
+      <c r="F16" s="141">
+        <v>0</v>
+      </c>
+      <c r="G16" s="141">
         <v>13.4</v>
       </c>
-      <c r="H16" s="145">
+      <c r="H16" s="142">
         <f t="shared" si="1"/>
         <v>13.4</v>
       </c>
-      <c r="I16" s="146">
+      <c r="I16" s="143">
         <f t="shared" si="2"/>
         <v>1474</v>
       </c>
-      <c r="J16" s="146">
+      <c r="J16" s="143">
         <f>J3*E16%</f>
         <v>0</v>
       </c>
-      <c r="K16" s="176">
+      <c r="K16" s="173">
         <f t="shared" si="3"/>
         <v>36307.014920194961</v>
       </c>
-      <c r="L16" s="147">
+      <c r="L16" s="144">
         <f t="shared" si="0"/>
         <v>13.4</v>
       </c>
-      <c r="M16" s="145">
+      <c r="M16" s="142">
         <f t="shared" si="4"/>
         <v>37781.014920194961</v>
       </c>
     </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A17" s="139">
+    <row r="17" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A17" s="136">
         <v>14</v>
       </c>
-      <c r="B17" s="150">
+      <c r="B17" s="147">
         <v>14</v>
       </c>
-      <c r="C17" s="141" t="str">
+      <c r="C17" s="138" t="str">
         <f>PRORRATEO!A18</f>
         <v>5A</v>
       </c>
-      <c r="D17" s="142" t="str">
+      <c r="D17" s="139" t="str">
         <f>PRORRATEO!B18</f>
         <v>Sr Propietario</v>
       </c>
-      <c r="E17" s="143">
+      <c r="E17" s="140">
         <v>12.127777780000001</v>
       </c>
-      <c r="F17" s="144">
-        <v>0</v>
-      </c>
-      <c r="G17" s="144">
+      <c r="F17" s="141">
+        <v>0</v>
+      </c>
+      <c r="G17" s="141">
         <v>4943.5</v>
       </c>
-      <c r="H17" s="145">
+      <c r="H17" s="142">
         <f t="shared" si="1"/>
         <v>4943.5</v>
       </c>
-      <c r="I17" s="146">
+      <c r="I17" s="143">
         <f t="shared" si="2"/>
         <v>543785</v>
       </c>
-      <c r="J17" s="146">
+      <c r="J17" s="143">
         <f>J3*E17%</f>
         <v>0</v>
       </c>
-      <c r="K17" s="176">
+      <c r="K17" s="173">
         <f t="shared" si="3"/>
         <v>104150.08350019496</v>
       </c>
-      <c r="L17" s="147">
+      <c r="L17" s="144">
         <f t="shared" si="0"/>
         <v>4943.5</v>
       </c>
-      <c r="M17" s="145">
+      <c r="M17" s="142">
         <f t="shared" si="4"/>
         <v>647935.08350019495</v>
       </c>
     </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A18" s="139">
+    <row r="18" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A18" s="136">
         <v>15</v>
       </c>
-      <c r="B18" s="150">
+      <c r="B18" s="147">
         <v>15</v>
       </c>
-      <c r="C18" s="141"/>
-      <c r="D18" s="142"/>
-      <c r="E18" s="143"/>
-      <c r="F18" s="144"/>
-      <c r="G18" s="144"/>
-      <c r="H18" s="145"/>
-      <c r="I18" s="146"/>
-      <c r="J18" s="146"/>
-      <c r="K18" s="176"/>
-      <c r="L18" s="147"/>
-      <c r="M18" s="145"/>
-    </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A19" s="139">
+      <c r="C18" s="138"/>
+      <c r="D18" s="139"/>
+      <c r="E18" s="140"/>
+      <c r="F18" s="141"/>
+      <c r="G18" s="141"/>
+      <c r="H18" s="142"/>
+      <c r="I18" s="143"/>
+      <c r="J18" s="143"/>
+      <c r="K18" s="173"/>
+      <c r="L18" s="144"/>
+      <c r="M18" s="142"/>
+    </row>
+    <row r="19" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A19" s="136">
         <v>16</v>
       </c>
-      <c r="B19" s="150">
+      <c r="B19" s="147">
         <v>16</v>
       </c>
-      <c r="C19" s="141" t="str">
+      <c r="C19" s="138" t="str">
         <f>PRORRATEO!A20</f>
         <v>C1</v>
       </c>
-      <c r="D19" s="142" t="str">
+      <c r="D19" s="139" t="str">
         <f>PRORRATEO!B20</f>
         <v>Frosio Diego Martin</v>
       </c>
-      <c r="E19" s="143">
+      <c r="E19" s="140">
         <v>2.2277777800000003</v>
       </c>
-      <c r="F19" s="144">
-        <v>0</v>
-      </c>
-      <c r="G19" s="144">
-        <v>0</v>
-      </c>
-      <c r="H19" s="145">
+      <c r="F19" s="141">
+        <v>0</v>
+      </c>
+      <c r="G19" s="141">
+        <v>0</v>
+      </c>
+      <c r="H19" s="142">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I19" s="146">
+      <c r="I19" s="143">
         <f t="shared" ref="I19:I21" si="5">L19*93.787</f>
         <v>0</v>
       </c>
-      <c r="J19" s="146">
+      <c r="J19" s="143">
         <f>J3*E19%</f>
         <v>0</v>
       </c>
-      <c r="K19" s="176">
+      <c r="K19" s="173">
         <f t="shared" si="3"/>
         <v>19131.554520194957</v>
       </c>
-      <c r="L19" s="147">
+      <c r="L19" s="144">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="M19" s="145">
+      <c r="M19" s="142">
         <f t="shared" si="4"/>
         <v>19131.554520194957</v>
       </c>
     </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A20" s="139">
+    <row r="20" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A20" s="136">
         <v>17</v>
       </c>
-      <c r="B20" s="150">
+      <c r="B20" s="147">
         <v>17</v>
       </c>
-      <c r="C20" s="141" t="str">
+      <c r="C20" s="138" t="str">
         <f>PRORRATEO!A21</f>
         <v>C2</v>
       </c>
-      <c r="D20" s="142" t="str">
+      <c r="D20" s="139" t="str">
         <f>PRORRATEO!B21</f>
         <v>Sr Propietario</v>
       </c>
-      <c r="E20" s="143">
+      <c r="E20" s="140">
         <v>2.2277777800000003</v>
       </c>
-      <c r="F20" s="144">
-        <v>0</v>
-      </c>
-      <c r="G20" s="144">
-        <v>0</v>
-      </c>
-      <c r="H20" s="145">
+      <c r="F20" s="141">
+        <v>0</v>
+      </c>
+      <c r="G20" s="141">
+        <v>0</v>
+      </c>
+      <c r="H20" s="142">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I20" s="146">
+      <c r="I20" s="143">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="J20" s="146">
+      <c r="J20" s="143">
         <f>J3*E20%</f>
         <v>0</v>
       </c>
-      <c r="K20" s="176">
+      <c r="K20" s="173">
         <f t="shared" si="3"/>
         <v>19131.554520194957</v>
       </c>
-      <c r="L20" s="147">
+      <c r="L20" s="144">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="M20" s="145">
+      <c r="M20" s="142">
         <f t="shared" si="4"/>
         <v>19131.554520194957</v>
       </c>
     </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A21" s="139">
+    <row r="21" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A21" s="136">
         <v>18</v>
       </c>
-      <c r="B21" s="150">
+      <c r="B21" s="147">
         <v>18</v>
       </c>
-      <c r="C21" s="141" t="str">
+      <c r="C21" s="138" t="str">
         <f>PRORRATEO!A22</f>
         <v>C3</v>
       </c>
-      <c r="D21" s="142" t="str">
+      <c r="D21" s="139" t="str">
         <f>PRORRATEO!B22</f>
         <v>Torres Lilliana Beatriz</v>
       </c>
-      <c r="E21" s="143">
+      <c r="E21" s="140">
         <v>2.2277777800000003</v>
       </c>
-      <c r="F21" s="144">
-        <v>0</v>
-      </c>
-      <c r="G21" s="144">
-        <v>0</v>
-      </c>
-      <c r="H21" s="145">
+      <c r="F21" s="141">
+        <v>0</v>
+      </c>
+      <c r="G21" s="141">
+        <v>0</v>
+      </c>
+      <c r="H21" s="142">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I21" s="146">
+      <c r="I21" s="143">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="J21" s="146">
+      <c r="J21" s="143">
         <f>J3*E21%</f>
         <v>0</v>
       </c>
-      <c r="K21" s="176">
+      <c r="K21" s="173">
         <f t="shared" si="3"/>
         <v>19131.554520194957</v>
       </c>
-      <c r="L21" s="147">
+      <c r="L21" s="144">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="M21" s="145">
+      <c r="M21" s="142">
         <f>I21+K21</f>
         <v>19131.554520194957</v>
       </c>
     </row>
-    <row r="22" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="139">
+    <row r="22" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="136">
         <v>19</v>
       </c>
-      <c r="B22" s="153">
+      <c r="B22" s="150">
         <v>19</v>
       </c>
-      <c r="C22" s="141" t="str">
+      <c r="C22" s="138" t="str">
         <f>PRORRATEO!A23</f>
         <v>C4</v>
       </c>
-      <c r="D22" s="142" t="str">
+      <c r="D22" s="139" t="str">
         <f>PRORRATEO!B23</f>
         <v>Frosio Diego Martin</v>
       </c>
-      <c r="E22" s="173">
+      <c r="E22" s="170">
         <v>2.2277777800000003</v>
       </c>
-      <c r="F22" s="144">
-        <v>0</v>
-      </c>
-      <c r="G22" s="144">
-        <v>0</v>
-      </c>
-      <c r="H22" s="145">
+      <c r="F22" s="141">
+        <v>0</v>
+      </c>
+      <c r="G22" s="141">
+        <v>0</v>
+      </c>
+      <c r="H22" s="142">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I22" s="146"/>
-      <c r="J22" s="146"/>
-      <c r="K22" s="176">
+      <c r="I22" s="143"/>
+      <c r="J22" s="143"/>
+      <c r="K22" s="173">
         <f t="shared" si="3"/>
         <v>19131.554520194957</v>
       </c>
-      <c r="L22" s="147">
-        <v>0</v>
-      </c>
-      <c r="M22" s="145">
+      <c r="L22" s="144">
+        <v>0</v>
+      </c>
+      <c r="M22" s="142">
         <f t="shared" ref="M22:M23" si="6">I22+K22</f>
         <v>19131.554520194957</v>
       </c>
     </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A23" s="139">
+    <row r="23" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A23" s="136">
         <v>20</v>
       </c>
-      <c r="B23" s="153"/>
-      <c r="C23" s="141" t="str">
+      <c r="B23" s="150"/>
+      <c r="C23" s="138" t="str">
         <f>PRORRATEO!A24</f>
         <v>C5</v>
       </c>
-      <c r="D23" s="142" t="str">
+      <c r="D23" s="139" t="str">
         <f>PRORRATEO!B24</f>
         <v>Sr Propietario</v>
       </c>
-      <c r="E23" s="154">
+      <c r="E23" s="151">
         <v>2.2277777800000003</v>
       </c>
-      <c r="F23" s="144">
-        <v>0</v>
-      </c>
-      <c r="G23" s="144">
-        <v>0</v>
-      </c>
-      <c r="H23" s="145">
-        <v>0</v>
-      </c>
-      <c r="I23" s="155"/>
-      <c r="J23" s="146"/>
-      <c r="K23" s="176">
+      <c r="F23" s="141">
+        <v>0</v>
+      </c>
+      <c r="G23" s="141">
+        <v>0</v>
+      </c>
+      <c r="H23" s="142">
+        <v>0</v>
+      </c>
+      <c r="I23" s="152"/>
+      <c r="J23" s="143"/>
+      <c r="K23" s="173">
         <f t="shared" si="3"/>
         <v>19131.554520194957</v>
       </c>
-      <c r="L23" s="147">
-        <v>0</v>
-      </c>
-      <c r="M23" s="145">
+      <c r="L23" s="144">
+        <v>0</v>
+      </c>
+      <c r="M23" s="142">
         <f t="shared" si="6"/>
         <v>19131.554520194957</v>
       </c>
     </row>
-    <row r="24" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="139">
+    <row r="24" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="136">
         <v>24</v>
       </c>
-      <c r="B24" s="153"/>
-      <c r="C24" s="156"/>
-      <c r="D24" s="156"/>
-      <c r="E24" s="185">
+      <c r="B24" s="150"/>
+      <c r="C24" s="153"/>
+      <c r="D24" s="153"/>
+      <c r="E24" s="182">
         <f>SUM(E5:E23)</f>
         <v>100.00000003999999</v>
       </c>
-      <c r="F24" s="156"/>
-      <c r="G24" s="156"/>
-      <c r="H24" s="157"/>
-      <c r="I24" s="158">
+      <c r="F24" s="153"/>
+      <c r="G24" s="153"/>
+      <c r="H24" s="154"/>
+      <c r="I24" s="155">
         <f>SUM(I5:I23)</f>
         <v>1662441</v>
       </c>
-      <c r="J24" s="175"/>
-      <c r="K24" s="175">
+      <c r="J24" s="172"/>
+      <c r="K24" s="172">
         <f>SUM(K5:K23)</f>
         <v>858773.0203435095</v>
       </c>
-      <c r="L24" s="159"/>
-      <c r="M24" s="157">
+      <c r="L24" s="156"/>
+      <c r="M24" s="154">
         <f>SUM(M5:M23)</f>
         <v>2521214.0203435086</v>
       </c>
       <c r="N24" s="39"/>
     </row>
-    <row r="25" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="123"/>
-      <c r="C25" s="160"/>
-      <c r="D25" s="161"/>
-      <c r="E25" s="162">
+    <row r="25" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="120"/>
+      <c r="C25" s="157"/>
+      <c r="D25" s="158"/>
+      <c r="E25" s="159">
         <f>SUM(E5:E24)</f>
         <v>200.00000007999998</v>
       </c>
-      <c r="F25" s="161"/>
-      <c r="G25" s="161"/>
-      <c r="H25" s="163"/>
-      <c r="I25" s="165"/>
-      <c r="J25" s="164"/>
-      <c r="K25" s="166">
+      <c r="F25" s="158"/>
+      <c r="G25" s="158"/>
+      <c r="H25" s="160"/>
+      <c r="I25" s="162"/>
+      <c r="J25" s="161"/>
+      <c r="K25" s="163">
         <f>K24+I24</f>
         <v>2521214.0203435095</v>
       </c>
-      <c r="L25" s="163"/>
-      <c r="M25" s="163"/>
-    </row>
-    <row r="26" spans="1:14" ht="30" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="168" t="s">
+      <c r="L25" s="160"/>
+      <c r="M25" s="160"/>
+    </row>
+    <row r="26" spans="1:14" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="165" t="s">
         <v>80</v>
       </c>
-      <c r="C26" s="220"/>
-      <c r="D26" s="217"/>
-      <c r="E26" s="217"/>
-      <c r="F26" s="217"/>
-      <c r="G26" s="217"/>
-      <c r="H26" s="217"/>
-      <c r="I26" s="217"/>
-      <c r="J26" s="217"/>
-      <c r="K26" s="217"/>
-      <c r="L26" s="217"/>
-      <c r="M26" s="217"/>
-    </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="H27" s="167"/>
-      <c r="I27" s="169"/>
-      <c r="J27" s="169"/>
-      <c r="K27" s="169"/>
-      <c r="M27" s="148"/>
-    </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="C26" s="215"/>
+      <c r="D26" s="212"/>
+      <c r="E26" s="212"/>
+      <c r="F26" s="212"/>
+      <c r="G26" s="212"/>
+      <c r="H26" s="212"/>
+      <c r="I26" s="212"/>
+      <c r="J26" s="212"/>
+      <c r="K26" s="212"/>
+      <c r="L26" s="212"/>
+      <c r="M26" s="212"/>
+    </row>
+    <row r="27" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="H27" s="164"/>
+      <c r="I27" s="166"/>
+      <c r="J27" s="166"/>
+      <c r="K27" s="166"/>
+      <c r="M27" s="145"/>
+    </row>
+    <row r="29" spans="1:14" x14ac:dyDescent="0.3">
       <c r="E29" s="2"/>
     </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="K30" s="170"/>
-    </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="K31" s="169"/>
-    </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="E32" s="171"/>
-      <c r="F32" s="171"/>
-      <c r="G32" s="171"/>
-      <c r="H32" s="171"/>
-      <c r="I32" s="171"/>
-      <c r="J32" s="171"/>
-      <c r="K32" s="172"/>
+    <row r="30" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="K30" s="167"/>
+    </row>
+    <row r="31" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="K31" s="166"/>
+    </row>
+    <row r="32" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="E32" s="168"/>
+      <c r="F32" s="168"/>
+      <c r="G32" s="168"/>
+      <c r="H32" s="168"/>
+      <c r="I32" s="168"/>
+      <c r="J32" s="168"/>
+      <c r="K32" s="169"/>
     </row>
   </sheetData>
   <mergeCells count="4">

--- a/2026/GAEBELER 1949/Marzo/Marzo Gaebeler.xlsx
+++ b/2026/GAEBELER 1949/Marzo/Marzo Gaebeler.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\2026\GAEBELER 1949\Marzo\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Escritorio\ARCHIVOS - CUESTIONES LABORALES\rc-consorcio2025\2026\GAEBELER 1949\Marzo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31B77347-9ECD-4647-A10D-63B0A37FBB8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B8227C1-288B-4B33-BA54-2A63DC4642A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="850" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="850" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="1" r:id="rId1"/>
@@ -22,12 +22,25 @@
     <definedName name="_xlnm.Print_Area" localSheetId="1">PRORRATEO!$A$1:$N$26</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$E$79</definedName>
   </definedNames>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="98">
   <si>
     <t>UF</t>
   </si>
@@ -315,9 +328,6 @@
   </si>
   <si>
     <t xml:space="preserve">Seguro integral de cosorcio - Federacion patronal - Poliza 2217080 </t>
-  </si>
-  <si>
-    <t>Transferencia no identificada Sra. Antonela Borgia 20/03</t>
   </si>
   <si>
     <t>VTO 06/04</t>
@@ -331,16 +341,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="10">
-    <numFmt numFmtId="8" formatCode="&quot;$&quot;\ #,##0.00;[Red]\-&quot;$&quot;\ #,##0.00"/>
-    <numFmt numFmtId="44" formatCode="_-&quot;$&quot;\ * #,##0.00_-;\-&quot;$&quot;\ * #,##0.00_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="164" formatCode="_ &quot;$&quot;\ * #,##0.00_ ;_ &quot;$&quot;\ * \-#,##0.00_ ;_ &quot;$&quot;\ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="165" formatCode="_-&quot;$&quot;\ * #,##0_-;\-&quot;$&quot;\ * #,##0_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="166" formatCode="_-&quot;$&quot;\ * #,##0.0_-;\-&quot;$&quot;\ * #,##0.0_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="167" formatCode="_-&quot;$&quot;\ * #,##0.0_-;\-&quot;$&quot;\ * #,##0.0_-;_-&quot;$&quot;\ * &quot;-&quot;?_-;_-@_-"/>
-    <numFmt numFmtId="168" formatCode="_-&quot;$&quot;\ * #,##0_-;\-&quot;$&quot;\ * #,##0_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@"/>
-    <numFmt numFmtId="169" formatCode="_-&quot;$&quot;\ * #,##0.00_-;\-&quot;$&quot;\ * #,##0.00_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@"/>
-    <numFmt numFmtId="170" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="164" formatCode="&quot;$&quot;\ #,##0.00;[Red]\-&quot;$&quot;\ #,##0.00"/>
+    <numFmt numFmtId="165" formatCode="_-&quot;$&quot;\ * #,##0.00_-;\-&quot;$&quot;\ * #,##0.00_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="166" formatCode="_ &quot;$&quot;\ * #,##0.00_ ;_ &quot;$&quot;\ * \-#,##0.00_ ;_ &quot;$&quot;\ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="167" formatCode="_-&quot;$&quot;\ * #,##0_-;\-&quot;$&quot;\ * #,##0_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="168" formatCode="_-&quot;$&quot;\ * #,##0.0_-;\-&quot;$&quot;\ * #,##0.0_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="169" formatCode="_-&quot;$&quot;\ * #,##0.0_-;\-&quot;$&quot;\ * #,##0.0_-;_-&quot;$&quot;\ * &quot;-&quot;?_-;_-@_-"/>
+    <numFmt numFmtId="170" formatCode="_-&quot;$&quot;\ * #,##0_-;\-&quot;$&quot;\ * #,##0_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@"/>
+    <numFmt numFmtId="171" formatCode="_-&quot;$&quot;\ * #,##0.00_-;\-&quot;$&quot;\ * #,##0.00_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@"/>
+    <numFmt numFmtId="172" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
   <fonts count="32" x14ac:knownFonts="1">
     <font>
@@ -1109,8 +1119,8 @@
   </borders>
   <cellStyleXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="166" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
@@ -1122,7 +1132,7 @@
     <xf numFmtId="0" fontId="2" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="8" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="2" fillId="5" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1134,9 +1144,9 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="8" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="4" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -1149,7 +1159,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="11" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -1159,36 +1169,36 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="3" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="3" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="44" fontId="9" fillId="6" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="9" fillId="6" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="13" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="13" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="44" fontId="14" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="14" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="44" fontId="0" fillId="3" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="165" fontId="0" fillId="3" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="44" fontId="7" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="0" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="14" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="14" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="15" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1196,29 +1206,29 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="6" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="6" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="44" fontId="18" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="18" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="14" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="14" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="18" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="18" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="18" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="18" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="18" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="14" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="14" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="18" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="18" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="18" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="4" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="44" fontId="14" fillId="4" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="14" fillId="4" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="6" fillId="7" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="12" fillId="8" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="6" fillId="7" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="12" fillId="8" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -1228,60 +1238,60 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="4" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="4" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="19" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="19" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="10" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="10" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="9" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="9" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="6" fillId="6" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="44" fontId="8" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="0" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="165" fontId="6" fillId="6" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="8" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="0" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="9" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="14" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="14" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="10" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="2" fillId="10" borderId="24" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="2" fillId="10" borderId="24" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="44" fontId="6" fillId="4" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="6" fillId="4" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="0" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="3" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="6" fillId="4" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="3" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="6" fillId="4" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="19" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1290,15 +1300,15 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="22" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="170" fontId="22" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="169" fontId="24" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="171" fontId="24" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="22" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="22" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="170" fontId="22" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="22" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="23" fillId="11" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1312,7 +1322,7 @@
     <xf numFmtId="0" fontId="26" fillId="11" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="168" fontId="26" fillId="11" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="170" fontId="26" fillId="11" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1333,10 +1343,10 @@
     <xf numFmtId="0" fontId="12" fillId="2" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="43" fontId="12" fillId="2" borderId="1" xfId="4" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="28" fillId="2" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="27" fillId="2" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="169" fontId="27" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="170" fontId="27" fillId="2" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="171" fontId="27" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="27" fillId="2" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="22" fillId="9" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -1353,36 +1363,36 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="2" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="169" fontId="27" fillId="2" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="171" fontId="27" fillId="2" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="27" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="27" fillId="0" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="169" fontId="27" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="27" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="170" fontId="27" fillId="0" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="171" fontId="27" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="170" fontId="27" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="172" fontId="22" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="170" fontId="22" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="22" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="169" fontId="22" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="169" fontId="22" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="169" fontId="27" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="22" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="171" fontId="22" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="171" fontId="22" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="171" fontId="27" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="170" fontId="22" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="23" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="171" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="44" fontId="2" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="2" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="43" fontId="12" fillId="2" borderId="2" xfId="4" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="26" fillId="11" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="169" fontId="27" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="169" fontId="29" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="169" fontId="27" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="171" fontId="27" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="171" fontId="29" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="171" fontId="27" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="2" fillId="4" borderId="39" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="2" fillId="4" borderId="39" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1391,15 +1401,16 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="170" fontId="27" fillId="0" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="18" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="10" fillId="8" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="9" fillId="6" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="172" fontId="27" fillId="0" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="18" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="10" fillId="8" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="9" fillId="6" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="31" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1430,6 +1441,24 @@
     <xf numFmtId="0" fontId="17" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1442,9 +1471,6 @@
     <xf numFmtId="0" fontId="15" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1454,39 +1480,23 @@
     <xf numFmtId="0" fontId="15" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="20" fillId="11" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="22" fillId="0" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="22" fillId="0" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="12" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="169" fontId="25" fillId="0" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="171" fontId="25" fillId="0" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="44" fontId="31" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Millares 2" xfId="4" xr:uid="{769376F3-FA42-4CBE-8FC6-971888C358BE}"/>
@@ -1854,20 +1864,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:M83"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="37.5546875" customWidth="1"/>
-    <col min="2" max="2" width="24.6640625" customWidth="1"/>
-    <col min="3" max="3" width="15.88671875" hidden="1" customWidth="1"/>
-    <col min="4" max="4" width="21.6640625" customWidth="1"/>
-    <col min="5" max="5" width="14.6640625" customWidth="1"/>
+    <col min="1" max="1" width="37.54296875" customWidth="1"/>
+    <col min="2" max="2" width="24.6328125" customWidth="1"/>
+    <col min="3" max="3" width="15.90625" hidden="1" customWidth="1"/>
+    <col min="4" max="4" width="21.6328125" customWidth="1"/>
+    <col min="5" max="5" width="14.6328125" customWidth="1"/>
     <col min="6" max="6" width="13" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.54296875" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="18" customWidth="1"/>
-    <col min="12" max="12" width="18.33203125" customWidth="1"/>
+    <col min="12" max="12" width="18.36328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" s="15"/>
       <c r="B1" s="60" t="s">
         <v>68</v>
@@ -1876,16 +1886,16 @@
       <c r="D1" s="60"/>
       <c r="E1" s="61"/>
     </row>
-    <row r="2" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="16"/>
-      <c r="B2" s="189" t="s">
+      <c r="B2" s="190" t="s">
         <v>19</v>
       </c>
-      <c r="C2" s="189"/>
-      <c r="D2" s="189"/>
-      <c r="E2" s="190"/>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="C2" s="190"/>
+      <c r="D2" s="190"/>
+      <c r="E2" s="191"/>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" s="16"/>
       <c r="B3" s="176" t="s">
         <v>25</v>
@@ -1894,7 +1904,7 @@
       <c r="D3" s="17"/>
       <c r="E3" s="18"/>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" s="16"/>
       <c r="B4" s="17" t="s">
         <v>84</v>
@@ -1903,7 +1913,7 @@
       <c r="D4" s="17"/>
       <c r="E4" s="18"/>
     </row>
-    <row r="5" spans="1:5" ht="35.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:5" ht="35.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="177" t="s">
         <v>83</v>
       </c>
@@ -1914,56 +1924,56 @@
       </c>
       <c r="E5" s="179"/>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B7" s="196" t="s">
-        <v>97</v>
-      </c>
-      <c r="C7" s="196"/>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B8" s="196"/>
-      <c r="C8" s="196"/>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B9" s="196"/>
-      <c r="C9" s="196"/>
-    </row>
-    <row r="12" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="195" t="s">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B7" s="197" t="s">
+        <v>96</v>
+      </c>
+      <c r="C7" s="197"/>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B8" s="197"/>
+      <c r="C8" s="197"/>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B9" s="197"/>
+      <c r="C9" s="197"/>
+    </row>
+    <row r="12" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="196" t="s">
         <v>28</v>
       </c>
-      <c r="B12" s="195"/>
-      <c r="C12" s="195"/>
-      <c r="D12" s="195"/>
-      <c r="E12" s="195"/>
-    </row>
-    <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="195"/>
-      <c r="B13" s="195"/>
-      <c r="C13" s="195"/>
-      <c r="D13" s="195"/>
-      <c r="E13" s="195"/>
-    </row>
-    <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="195"/>
-      <c r="B14" s="195"/>
-      <c r="C14" s="195"/>
-      <c r="D14" s="195"/>
-      <c r="E14" s="195"/>
-    </row>
-    <row r="15" spans="1:5" ht="53.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="195"/>
-      <c r="B15" s="195"/>
-      <c r="C15" s="195"/>
-      <c r="D15" s="195"/>
-      <c r="E15" s="195"/>
-    </row>
-    <row r="16" spans="1:5" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="17" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B12" s="196"/>
+      <c r="C12" s="196"/>
+      <c r="D12" s="196"/>
+      <c r="E12" s="196"/>
+    </row>
+    <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="196"/>
+      <c r="B13" s="196"/>
+      <c r="C13" s="196"/>
+      <c r="D13" s="196"/>
+      <c r="E13" s="196"/>
+    </row>
+    <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="196"/>
+      <c r="B14" s="196"/>
+      <c r="C14" s="196"/>
+      <c r="D14" s="196"/>
+      <c r="E14" s="196"/>
+    </row>
+    <row r="15" spans="1:5" ht="53.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="196"/>
+      <c r="B15" s="196"/>
+      <c r="C15" s="196"/>
+      <c r="D15" s="196"/>
+      <c r="E15" s="196"/>
+    </row>
+    <row r="16" spans="1:5" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="17" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A17" s="2"/>
     </row>
-    <row r="18" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A19" s="11" t="s">
         <v>5</v>
       </c>
@@ -1972,7 +1982,7 @@
       <c r="D19" s="9"/>
       <c r="E19" s="14"/>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A20" s="31" t="s">
         <v>81</v>
       </c>
@@ -1981,29 +1991,29 @@
       <c r="D20" s="112"/>
       <c r="E20" s="113"/>
     </row>
-    <row r="21" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="187" t="s">
+    <row r="21" spans="1:7" ht="35.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="188" t="s">
         <v>95</v>
       </c>
-      <c r="B21" s="188"/>
+      <c r="B21" s="189"/>
       <c r="C21" s="5"/>
       <c r="D21" s="183">
         <v>52745</v>
       </c>
       <c r="E21" s="115"/>
     </row>
-    <row r="22" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="187" t="s">
+    <row r="22" spans="1:7" ht="35.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="188" t="s">
         <v>94</v>
       </c>
-      <c r="B22" s="188"/>
+      <c r="B22" s="189"/>
       <c r="C22" s="5"/>
       <c r="D22" s="183">
         <v>496816.96</v>
       </c>
       <c r="E22" s="115"/>
     </row>
-    <row r="23" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A23" s="26" t="s">
         <v>82</v>
       </c>
@@ -2015,7 +2025,7 @@
         <v>549561.96</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A24" s="26" t="s">
         <v>4</v>
       </c>
@@ -2027,29 +2037,29 @@
         <v>549561.96</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A25" s="5"/>
       <c r="B25" s="5"/>
       <c r="C25" s="5"/>
       <c r="D25" s="78"/>
       <c r="E25" s="84"/>
     </row>
-    <row r="26" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A26" s="27" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B26" s="27"/>
       <c r="C26" s="27"/>
       <c r="D26" s="85"/>
       <c r="E26" s="185"/>
     </row>
-    <row r="27" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A27" s="1"/>
       <c r="D27" s="86"/>
       <c r="E27" s="87"/>
       <c r="F27" s="39"/>
     </row>
-    <row r="28" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A28" s="3" t="s">
         <v>7</v>
       </c>
@@ -2063,15 +2073,15 @@
       <c r="F28" s="109"/>
       <c r="G28" s="39"/>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.35">
       <c r="D29" s="86"/>
       <c r="E29" s="86"/>
     </row>
-    <row r="30" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="D30" s="86"/>
       <c r="E30" s="86"/>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A31" s="11" t="s">
         <v>30</v>
       </c>
@@ -2080,35 +2090,35 @@
       <c r="D31" s="90"/>
       <c r="E31" s="91"/>
     </row>
-    <row r="32" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="187"/>
-      <c r="B32" s="188"/>
+    <row r="32" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A32" s="188"/>
+      <c r="B32" s="189"/>
       <c r="C32" s="5"/>
       <c r="D32" s="98"/>
       <c r="E32" s="79"/>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A33" s="187"/>
-      <c r="B33" s="188"/>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A33" s="188"/>
+      <c r="B33" s="189"/>
       <c r="C33" s="5"/>
       <c r="D33" s="81"/>
       <c r="E33" s="79"/>
     </row>
-    <row r="34" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="193"/>
-      <c r="B34" s="194"/>
+    <row r="34" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A34" s="194"/>
+      <c r="B34" s="195"/>
       <c r="C34" s="5"/>
       <c r="D34" s="81"/>
       <c r="E34" s="79"/>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A35" s="80"/>
       <c r="B35" s="82"/>
       <c r="C35" s="5"/>
       <c r="D35" s="81"/>
       <c r="E35" s="79"/>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A36" s="45"/>
       <c r="B36" s="44"/>
       <c r="C36" s="44"/>
@@ -2118,9 +2128,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="38" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="39" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="38" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="39" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A39" s="27" t="s">
         <v>10</v>
       </c>
@@ -2129,8 +2139,8 @@
       <c r="D39" s="28"/>
       <c r="E39" s="77"/>
     </row>
-    <row r="40" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="41" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="41" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A41" s="3" t="s">
         <v>11</v>
       </c>
@@ -2142,8 +2152,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="43" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="43" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A43" s="75" t="s">
         <v>8</v>
       </c>
@@ -2152,7 +2162,7 @@
         <v>549561.96</v>
       </c>
     </row>
-    <row r="44" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A44" s="75" t="s">
         <v>9</v>
       </c>
@@ -2161,7 +2171,7 @@
         <v>549561.96</v>
       </c>
     </row>
-    <row r="45" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A45" s="75" t="s">
         <v>12</v>
       </c>
@@ -2170,7 +2180,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A46" s="75" t="s">
         <v>26</v>
       </c>
@@ -2179,44 +2189,44 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:5" ht="73.5" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="48" spans="1:5" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="49" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="191"/>
-      <c r="B49" s="191"/>
-      <c r="C49" s="191"/>
-      <c r="D49" s="191"/>
-      <c r="E49" s="191"/>
-    </row>
-    <row r="50" spans="1:6" ht="106.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="191"/>
-      <c r="B50" s="191"/>
-      <c r="C50" s="191"/>
-      <c r="D50" s="191"/>
-      <c r="E50" s="191"/>
-    </row>
-    <row r="51" spans="1:6" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="191"/>
-      <c r="B51" s="191"/>
-      <c r="C51" s="191"/>
-      <c r="D51" s="191"/>
-      <c r="E51" s="191"/>
-    </row>
-    <row r="53" spans="1:6" ht="0.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:5" ht="73.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="48" spans="1:5" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="49" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A49" s="192"/>
+      <c r="B49" s="192"/>
+      <c r="C49" s="192"/>
+      <c r="D49" s="192"/>
+      <c r="E49" s="192"/>
+    </row>
+    <row r="50" spans="1:6" ht="106.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A50" s="192"/>
+      <c r="B50" s="192"/>
+      <c r="C50" s="192"/>
+      <c r="D50" s="192"/>
+      <c r="E50" s="192"/>
+    </row>
+    <row r="51" spans="1:6" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A51" s="192"/>
+      <c r="B51" s="192"/>
+      <c r="C51" s="192"/>
+      <c r="D51" s="192"/>
+      <c r="E51" s="192"/>
+    </row>
+    <row r="53" spans="1:6" ht="0.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A53" s="20" t="s">
         <v>22</v>
       </c>
       <c r="B53" s="95"/>
       <c r="C53" s="21"/>
     </row>
-    <row r="54" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A54" s="30"/>
       <c r="B54" s="52">
         <v>0</v>
       </c>
       <c r="C54" s="23"/>
     </row>
-    <row r="55" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A55" s="22" t="s">
         <v>2</v>
       </c>
@@ -2226,36 +2236,36 @@
       </c>
       <c r="C55" s="21"/>
     </row>
-    <row r="56" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A56" s="22"/>
       <c r="B56" s="36">
         <v>0</v>
       </c>
       <c r="C56" s="21"/>
     </row>
-    <row r="57" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A57" s="22" t="s">
         <v>27</v>
       </c>
       <c r="B57" s="83">
         <f>B78</f>
-        <v>165459</v>
+        <v>0</v>
       </c>
       <c r="C57" s="21"/>
     </row>
-    <row r="58" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A58" s="25"/>
       <c r="B58" s="43"/>
       <c r="C58" s="21"/>
     </row>
-    <row r="59" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A59" s="94" t="s">
         <v>31</v>
       </c>
       <c r="B59" s="43"/>
       <c r="C59" s="21"/>
     </row>
-    <row r="60" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A60" s="35" t="s">
         <v>13</v>
       </c>
@@ -2265,7 +2275,7 @@
       </c>
       <c r="C60" s="21"/>
     </row>
-    <row r="61" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A61" s="25" t="s">
         <v>14</v>
       </c>
@@ -2275,34 +2285,34 @@
       </c>
       <c r="C61" s="21"/>
     </row>
-    <row r="62" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A62" s="29" t="s">
         <v>4</v>
       </c>
       <c r="B62" s="52">
         <f>SUM(B54:B61)</f>
-        <v>602565.33000000007</v>
+        <v>437106.33000000007</v>
       </c>
       <c r="C62" s="24"/>
       <c r="D62" s="39"/>
     </row>
-    <row r="63" spans="1:6" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:6" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B63" s="37"/>
       <c r="C63" s="24"/>
       <c r="D63" s="39"/>
       <c r="E63" s="96"/>
       <c r="F63" s="97"/>
     </row>
-    <row r="64" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B64" s="38"/>
       <c r="C64" s="24"/>
     </row>
-    <row r="65" spans="1:13" s="34" customFormat="1" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:13" s="34" customFormat="1" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A65"/>
       <c r="B65" s="37"/>
       <c r="C65" s="33"/>
     </row>
-    <row r="66" spans="1:13" s="34" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:13" s="34" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A66" s="100" t="s">
         <v>91</v>
       </c>
@@ -2312,7 +2322,7 @@
       <c r="C66" s="33"/>
       <c r="D66" s="42"/>
     </row>
-    <row r="67" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A67" s="48" t="s">
         <v>34</v>
       </c>
@@ -2321,7 +2331,7 @@
         <v>-549561.96</v>
       </c>
     </row>
-    <row r="68" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A68" s="48" t="s">
         <v>35</v>
       </c>
@@ -2330,20 +2340,17 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A69" s="48" t="s">
         <v>39</v>
       </c>
       <c r="B69" s="105">
         <f>B78</f>
-        <v>165459</v>
-      </c>
-      <c r="D69" s="39">
-        <f>B69+B70</f>
-        <v>1152127.29</v>
-      </c>
-    </row>
-    <row r="70" spans="1:13" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+      <c r="D69" s="39"/>
+    </row>
+    <row r="70" spans="1:13" ht="14" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A70" s="48" t="s">
         <v>36</v>
       </c>
@@ -2352,90 +2359,86 @@
         <v>986668.29</v>
       </c>
     </row>
-    <row r="71" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A71" s="107" t="s">
         <v>37</v>
       </c>
       <c r="B71" s="108"/>
     </row>
-    <row r="72" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A72" s="103" t="s">
         <v>32</v>
       </c>
       <c r="B72" s="104">
         <f>SUM(B66:C71)</f>
-        <v>-2132618.63</v>
-      </c>
-    </row>
-    <row r="73" spans="1:13" x14ac:dyDescent="0.3">
+        <v>-2298077.63</v>
+      </c>
+    </row>
+    <row r="73" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A73" s="101"/>
       <c r="B73" s="101"/>
     </row>
-    <row r="74" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="75" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A75" s="192" t="s">
+    <row r="74" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="75" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A75" s="193" t="s">
         <v>21</v>
       </c>
-      <c r="B75" s="192"/>
-      <c r="C75" s="192"/>
-    </row>
-    <row r="76" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A76" s="192"/>
-      <c r="B76" s="192"/>
-      <c r="C76" s="192"/>
-    </row>
-    <row r="77" spans="1:13" ht="35.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A77" s="92" t="s">
-        <v>96</v>
-      </c>
-      <c r="B77" s="32">
-        <v>165459</v>
-      </c>
+      <c r="B75" s="193"/>
+      <c r="C75" s="193"/>
+    </row>
+    <row r="76" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A76" s="193"/>
+      <c r="B76" s="193"/>
+      <c r="C76" s="193"/>
+    </row>
+    <row r="77" spans="1:13" ht="35.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A77" s="92"/>
+      <c r="B77" s="32"/>
       <c r="C77" s="32">
         <v>40000</v>
       </c>
       <c r="E77" s="109"/>
     </row>
-    <row r="78" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A78" s="40" t="s">
         <v>4</v>
       </c>
       <c r="B78" s="93">
         <f>SUM(B77:B77)</f>
-        <v>165459</v>
+        <v>0</v>
       </c>
       <c r="C78" s="41"/>
     </row>
-    <row r="79" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:13" x14ac:dyDescent="0.35">
       <c r="M79" s="8"/>
     </row>
-    <row r="80" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A80" s="191"/>
-      <c r="B80" s="191"/>
-      <c r="C80" s="191"/>
-      <c r="D80" s="191"/>
-      <c r="E80" s="191"/>
-    </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A81" s="191"/>
-      <c r="B81" s="191"/>
-      <c r="C81" s="191"/>
-      <c r="D81" s="191"/>
-      <c r="E81" s="191"/>
-    </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A82" s="191"/>
-      <c r="B82" s="191"/>
-      <c r="C82" s="191"/>
-      <c r="D82" s="191"/>
-      <c r="E82" s="191"/>
-    </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A83" s="191"/>
-      <c r="B83" s="191"/>
-      <c r="C83" s="191"/>
-      <c r="D83" s="191"/>
-      <c r="E83" s="191"/>
+    <row r="80" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A80" s="192"/>
+      <c r="B80" s="192"/>
+      <c r="C80" s="192"/>
+      <c r="D80" s="192"/>
+      <c r="E80" s="192"/>
+    </row>
+    <row r="81" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A81" s="192"/>
+      <c r="B81" s="192"/>
+      <c r="C81" s="192"/>
+      <c r="D81" s="192"/>
+      <c r="E81" s="192"/>
+    </row>
+    <row r="82" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A82" s="192"/>
+      <c r="B82" s="192"/>
+      <c r="C82" s="192"/>
+      <c r="D82" s="192"/>
+      <c r="E82" s="192"/>
+    </row>
+    <row r="83" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A83" s="192"/>
+      <c r="B83" s="192"/>
+      <c r="C83" s="192"/>
+      <c r="D83" s="192"/>
+      <c r="E83" s="192"/>
     </row>
   </sheetData>
   <mergeCells count="11">
@@ -2460,28 +2463,28 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:Q30"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="4.33203125" customWidth="1"/>
-    <col min="2" max="2" width="18.5546875" customWidth="1"/>
-    <col min="3" max="3" width="0.109375" customWidth="1"/>
-    <col min="4" max="4" width="8.44140625" customWidth="1"/>
-    <col min="5" max="5" width="14.109375" customWidth="1"/>
-    <col min="6" max="6" width="12.33203125" customWidth="1"/>
-    <col min="7" max="7" width="7.6640625" hidden="1" customWidth="1"/>
-    <col min="8" max="8" width="10.5546875" customWidth="1"/>
-    <col min="9" max="9" width="9.5546875" customWidth="1"/>
-    <col min="10" max="10" width="0.109375" customWidth="1"/>
-    <col min="11" max="11" width="12.44140625" customWidth="1"/>
-    <col min="12" max="12" width="14.6640625" customWidth="1"/>
-    <col min="13" max="13" width="0.44140625" hidden="1" customWidth="1"/>
-    <col min="14" max="14" width="14.33203125" customWidth="1"/>
-    <col min="15" max="15" width="7.109375" hidden="1" customWidth="1"/>
+    <col min="1" max="1" width="4.36328125" customWidth="1"/>
+    <col min="2" max="2" width="18.54296875" customWidth="1"/>
+    <col min="3" max="3" width="8.984375E-2" customWidth="1"/>
+    <col min="4" max="4" width="8.453125" customWidth="1"/>
+    <col min="5" max="5" width="14.08984375" customWidth="1"/>
+    <col min="6" max="6" width="12.36328125" customWidth="1"/>
+    <col min="7" max="7" width="7.6328125" hidden="1" customWidth="1"/>
+    <col min="8" max="8" width="10.54296875" customWidth="1"/>
+    <col min="9" max="9" width="9.54296875" customWidth="1"/>
+    <col min="10" max="10" width="8.984375E-2" customWidth="1"/>
+    <col min="11" max="11" width="12.453125" customWidth="1"/>
+    <col min="12" max="12" width="14.6328125" customWidth="1"/>
+    <col min="13" max="13" width="0.453125" hidden="1" customWidth="1"/>
+    <col min="14" max="14" width="14.36328125" customWidth="1"/>
+    <col min="15" max="15" width="7.08984375" hidden="1" customWidth="1"/>
     <col min="16" max="16" width="12" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:17" ht="12.9" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="6"/>
       <c r="B1" s="17" t="str">
         <f>RESUMEN!B4</f>
@@ -2500,17 +2503,17 @@
       <c r="M1" s="6"/>
       <c r="N1" s="6"/>
     </row>
-    <row r="2" spans="1:17" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:17" ht="12.9" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="6"/>
-      <c r="B2" s="197" t="s">
+      <c r="B2" s="204" t="s">
         <v>86</v>
       </c>
-      <c r="C2" s="197"/>
-      <c r="D2" s="197"/>
-      <c r="E2" s="197"/>
-      <c r="F2" s="197"/>
-      <c r="G2" s="197"/>
-      <c r="H2" s="197"/>
+      <c r="C2" s="204"/>
+      <c r="D2" s="204"/>
+      <c r="E2" s="204"/>
+      <c r="F2" s="204"/>
+      <c r="G2" s="204"/>
+      <c r="H2" s="204"/>
       <c r="I2" s="6"/>
       <c r="J2" s="7"/>
       <c r="K2" s="6" t="s">
@@ -2523,15 +2526,15 @@
       <c r="N2" s="49"/>
       <c r="O2" s="19"/>
     </row>
-    <row r="3" spans="1:17" ht="12.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:17" ht="12.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A3" s="6"/>
-      <c r="B3" s="198"/>
-      <c r="C3" s="198"/>
-      <c r="D3" s="198"/>
-      <c r="E3" s="198"/>
-      <c r="F3" s="198"/>
-      <c r="G3" s="198"/>
-      <c r="H3" s="198"/>
+      <c r="B3" s="205"/>
+      <c r="C3" s="205"/>
+      <c r="D3" s="205"/>
+      <c r="E3" s="205"/>
+      <c r="F3" s="205"/>
+      <c r="G3" s="205"/>
+      <c r="H3" s="205"/>
       <c r="I3" s="6"/>
       <c r="J3" s="6"/>
       <c r="K3" s="6"/>
@@ -2539,71 +2542,71 @@
       <c r="M3" s="50"/>
       <c r="N3" s="53"/>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A4" s="201" t="s">
-        <v>0</v>
-      </c>
-      <c r="B4" s="201" t="s">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A4" s="198" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4" s="198" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="201" t="s">
+      <c r="C4" s="198" t="s">
         <v>17</v>
       </c>
-      <c r="D4" s="201" t="s">
+      <c r="D4" s="198" t="s">
         <v>6</v>
       </c>
-      <c r="E4" s="205" t="s">
+      <c r="E4" s="200" t="s">
         <v>33</v>
       </c>
-      <c r="F4" s="201" t="s">
+      <c r="F4" s="198" t="s">
         <v>2</v>
       </c>
-      <c r="G4" s="201" t="s">
+      <c r="G4" s="198" t="s">
         <v>18</v>
       </c>
-      <c r="H4" s="209" t="s">
+      <c r="H4" s="202" t="s">
         <v>20</v>
       </c>
-      <c r="I4" s="205" t="s">
+      <c r="I4" s="200" t="s">
         <v>29</v>
       </c>
-      <c r="J4" s="205" t="s">
+      <c r="J4" s="200" t="s">
         <v>3</v>
       </c>
-      <c r="K4" s="205" t="s">
+      <c r="K4" s="200" t="s">
         <v>16</v>
       </c>
       <c r="L4" s="56" t="s">
         <v>24</v>
       </c>
-      <c r="M4" s="203" t="s">
+      <c r="M4" s="209" t="s">
         <v>15</v>
       </c>
-      <c r="N4" s="199" t="s">
+      <c r="N4" s="206" t="s">
         <v>23</v>
       </c>
       <c r="Q4" s="39"/>
     </row>
-    <row r="5" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="208"/>
-      <c r="B5" s="208"/>
-      <c r="C5" s="202"/>
-      <c r="D5" s="208"/>
-      <c r="E5" s="207"/>
-      <c r="F5" s="208"/>
-      <c r="G5" s="202"/>
-      <c r="H5" s="210"/>
-      <c r="I5" s="207"/>
-      <c r="J5" s="206"/>
-      <c r="K5" s="207"/>
+    <row r="5" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="199"/>
+      <c r="B5" s="199"/>
+      <c r="C5" s="208"/>
+      <c r="D5" s="199"/>
+      <c r="E5" s="201"/>
+      <c r="F5" s="199"/>
+      <c r="G5" s="208"/>
+      <c r="H5" s="203"/>
+      <c r="I5" s="201"/>
+      <c r="J5" s="211"/>
+      <c r="K5" s="201"/>
       <c r="L5" s="54" t="str">
         <f>RESUMEN!B7</f>
         <v>VTO 06/04</v>
       </c>
-      <c r="M5" s="204"/>
-      <c r="N5" s="200"/>
-    </row>
-    <row r="6" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M5" s="210"/>
+      <c r="N5" s="207"/>
+    </row>
+    <row r="6" spans="1:17" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="57" t="s">
         <v>44</v>
       </c>
@@ -2618,7 +2621,7 @@
       <c r="E6" s="63">
         <v>260082.01</v>
       </c>
-      <c r="F6" s="217"/>
+      <c r="F6" s="187"/>
       <c r="G6" s="64"/>
       <c r="H6" s="65">
         <f>E6-F6</f>
@@ -2636,7 +2639,7 @@
         <v>99801.180580122003</v>
       </c>
       <c r="L6" s="68">
-        <f>ROUND(SUM(H6:K6),0) + O6</f>
+        <f t="shared" ref="L6:L18" si="0">ROUND(SUM(H6:K6),0) + O6</f>
         <v>367686.01</v>
       </c>
       <c r="M6" s="69">
@@ -2651,7 +2654,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="7" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:17" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="57" t="s">
         <v>45</v>
       </c>
@@ -2672,30 +2675,30 @@
       </c>
       <c r="G7" s="64"/>
       <c r="H7" s="65">
-        <f t="shared" ref="H7:H24" si="0">E7-F7</f>
+        <f t="shared" ref="H7:H24" si="1">E7-F7</f>
         <v>0</v>
       </c>
       <c r="I7" s="65">
-        <f t="shared" ref="I7:I24" si="1">IF(H7&gt;0,H7*3%,0)</f>
+        <f t="shared" ref="I7:I24" si="2">IF(H7&gt;0,H7*3%,0)</f>
         <v>0</v>
       </c>
       <c r="J7" s="66">
         <v>0</v>
       </c>
       <c r="K7" s="67">
-        <f>L$2*D7%</f>
+        <f t="shared" ref="K7:K18" si="3">L$2*D7%</f>
         <v>65530.990580122008</v>
       </c>
       <c r="L7" s="68">
-        <f>ROUND(SUM(H7:K7),0) + O7</f>
+        <f t="shared" si="0"/>
         <v>65531.02</v>
       </c>
       <c r="M7" s="69">
-        <f t="shared" ref="M7:M24" si="2">ROUND(L7*6% + L7,0) + O7</f>
+        <f t="shared" ref="M7:M24" si="4">ROUND(L7*6% + L7,0) + O7</f>
         <v>69463.02</v>
       </c>
       <c r="N7" s="70">
-        <f t="shared" ref="N7:N24" si="3">ROUND(L7*3%,0) + L7</f>
+        <f t="shared" ref="N7:N24" si="5">ROUND(L7*3%,0) + L7</f>
         <v>67497.01999999999</v>
       </c>
       <c r="O7" s="39">
@@ -2706,7 +2709,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="8" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:17" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="57" t="s">
         <v>47</v>
       </c>
@@ -2726,38 +2729,38 @@
       </c>
       <c r="G8" s="64"/>
       <c r="H8" s="65">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I8" s="65">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="J8" s="66">
+        <v>0</v>
+      </c>
+      <c r="K8" s="67">
+        <f t="shared" si="3"/>
+        <v>46737.660580121999</v>
+      </c>
+      <c r="L8" s="68">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I8" s="65">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="J8" s="66">
-        <v>0</v>
-      </c>
-      <c r="K8" s="67">
-        <f>L$2*D8%</f>
-        <v>46737.660580121999</v>
-      </c>
-      <c r="L8" s="68">
-        <f>ROUND(SUM(H8:K8),0) + O8</f>
         <v>46738.03</v>
       </c>
       <c r="M8" s="69">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>49542.03</v>
       </c>
       <c r="N8" s="70">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>48140.03</v>
       </c>
       <c r="O8" s="39">
-        <f t="shared" ref="O8:O24" si="4">O7+0.01</f>
+        <f t="shared" ref="O8:O24" si="6">O7+0.01</f>
         <v>0.03</v>
       </c>
     </row>
-    <row r="9" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:17" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="57" t="s">
         <v>48</v>
       </c>
@@ -2775,39 +2778,39 @@
       <c r="F9" s="64"/>
       <c r="G9" s="64"/>
       <c r="H9" s="65">
+        <f t="shared" si="1"/>
+        <v>216502.04</v>
+      </c>
+      <c r="I9" s="65">
+        <f t="shared" si="2"/>
+        <v>6495.0612000000001</v>
+      </c>
+      <c r="J9" s="66">
+        <v>0</v>
+      </c>
+      <c r="K9" s="67">
+        <f t="shared" si="3"/>
+        <v>99801.180580122018</v>
+      </c>
+      <c r="L9" s="68">
         <f t="shared" si="0"/>
-        <v>216502.04</v>
-      </c>
-      <c r="I9" s="65">
-        <f t="shared" si="1"/>
-        <v>6495.0612000000001</v>
-      </c>
-      <c r="J9" s="66">
-        <v>0</v>
-      </c>
-      <c r="K9" s="67">
-        <f>L$2*D9%</f>
-        <v>99801.180580122018</v>
-      </c>
-      <c r="L9" s="68">
-        <f>ROUND(SUM(H9:K9),0) + O9</f>
         <v>322798.03999999998</v>
       </c>
       <c r="M9" s="69">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>342166.04</v>
       </c>
       <c r="N9" s="70">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>332482.03999999998</v>
       </c>
       <c r="O9" s="39">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0.04</v>
       </c>
       <c r="Q9" s="39"/>
     </row>
-    <row r="10" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:17" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="57" t="s">
         <v>49</v>
       </c>
@@ -2825,39 +2828,39 @@
       <c r="F10" s="64"/>
       <c r="G10" s="64"/>
       <c r="H10" s="65">
+        <f t="shared" si="1"/>
+        <v>165458.04999999999</v>
+      </c>
+      <c r="I10" s="65">
+        <f t="shared" si="2"/>
+        <v>4963.7414999999992</v>
+      </c>
+      <c r="J10" s="66">
+        <v>0</v>
+      </c>
+      <c r="K10" s="67">
+        <f t="shared" si="3"/>
+        <v>65530.990580122008</v>
+      </c>
+      <c r="L10" s="68">
         <f t="shared" si="0"/>
-        <v>165458.04999999999</v>
-      </c>
-      <c r="I10" s="65">
-        <f t="shared" si="1"/>
-        <v>4963.7414999999992</v>
-      </c>
-      <c r="J10" s="66">
-        <v>0</v>
-      </c>
-      <c r="K10" s="67">
-        <f>L$2*D10%</f>
-        <v>65530.990580122008</v>
-      </c>
-      <c r="L10" s="68">
-        <f>ROUND(SUM(H10:K10),0) + O10</f>
         <v>235953.05</v>
       </c>
       <c r="M10" s="69">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>250110.05</v>
       </c>
       <c r="N10" s="70">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>243032.05</v>
       </c>
       <c r="O10" s="39">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0.05</v>
       </c>
       <c r="Q10" s="39"/>
     </row>
-    <row r="11" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:17" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="57" t="s">
         <v>50</v>
       </c>
@@ -2878,41 +2881,41 @@
       </c>
       <c r="G11" s="64"/>
       <c r="H11" s="65">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I11" s="65">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="J11" s="66">
+        <v>0</v>
+      </c>
+      <c r="K11" s="67">
+        <f t="shared" si="3"/>
+        <v>46737.660580121999</v>
+      </c>
+      <c r="L11" s="68">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I11" s="65">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="J11" s="66">
-        <v>0</v>
-      </c>
-      <c r="K11" s="67">
-        <f>L$2*D11%</f>
-        <v>46737.660580121999</v>
-      </c>
-      <c r="L11" s="68">
-        <f>ROUND(SUM(H11:K11),0) + O11</f>
         <v>46738.06</v>
       </c>
       <c r="M11" s="69">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>49542.06</v>
       </c>
       <c r="N11" s="70">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>48140.06</v>
       </c>
       <c r="O11" s="39">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>6.0000000000000005E-2</v>
       </c>
       <c r="P11" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="12" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:17" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="57" t="s">
         <v>51</v>
       </c>
@@ -2930,38 +2933,38 @@
       <c r="F12" s="64"/>
       <c r="G12" s="64"/>
       <c r="H12" s="65">
+        <f t="shared" si="1"/>
+        <v>211871.07</v>
+      </c>
+      <c r="I12" s="65">
+        <f t="shared" si="2"/>
+        <v>6356.1320999999998</v>
+      </c>
+      <c r="J12" s="66">
+        <v>0</v>
+      </c>
+      <c r="K12" s="67">
+        <f t="shared" si="3"/>
+        <v>99801.180580122018</v>
+      </c>
+      <c r="L12" s="68">
         <f t="shared" si="0"/>
-        <v>211871.07</v>
-      </c>
-      <c r="I12" s="65">
-        <f t="shared" si="1"/>
-        <v>6356.1320999999998</v>
-      </c>
-      <c r="J12" s="66">
-        <v>0</v>
-      </c>
-      <c r="K12" s="67">
-        <f>L$2*D12%</f>
-        <v>99801.180580122018</v>
-      </c>
-      <c r="L12" s="68">
-        <f>ROUND(SUM(H12:K12),0) + O12</f>
         <v>318028.07</v>
       </c>
       <c r="M12" s="69">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>337110.07</v>
       </c>
       <c r="N12" s="70">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>327569.07</v>
       </c>
       <c r="O12" s="39">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:17" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="57" t="s">
         <v>53</v>
       </c>
@@ -2979,38 +2982,38 @@
       <c r="F13" s="184"/>
       <c r="G13" s="64"/>
       <c r="H13" s="65">
+        <f t="shared" si="1"/>
+        <v>286943.08</v>
+      </c>
+      <c r="I13" s="65">
+        <f t="shared" si="2"/>
+        <v>8608.2924000000003</v>
+      </c>
+      <c r="J13" s="66">
+        <v>0</v>
+      </c>
+      <c r="K13" s="67">
+        <f t="shared" si="3"/>
+        <v>65530.990580122008</v>
+      </c>
+      <c r="L13" s="68">
         <f t="shared" si="0"/>
-        <v>286943.08</v>
-      </c>
-      <c r="I13" s="65">
-        <f t="shared" si="1"/>
-        <v>8608.2924000000003</v>
-      </c>
-      <c r="J13" s="66">
-        <v>0</v>
-      </c>
-      <c r="K13" s="67">
-        <f>L$2*D13%</f>
-        <v>65530.990580122008</v>
-      </c>
-      <c r="L13" s="68">
-        <f>ROUND(SUM(H13:K13),0) + O13</f>
         <v>361082.08</v>
       </c>
       <c r="M13" s="69">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>382747.08</v>
       </c>
       <c r="N13" s="70">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>371914.08</v>
       </c>
       <c r="O13" s="39">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0.08</v>
       </c>
     </row>
-    <row r="14" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:17" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="57" t="s">
         <v>54</v>
       </c>
@@ -3028,41 +3031,41 @@
       <c r="F14" s="184"/>
       <c r="G14" s="64"/>
       <c r="H14" s="65">
+        <f t="shared" si="1"/>
+        <v>156615.09</v>
+      </c>
+      <c r="I14" s="65">
+        <f t="shared" si="2"/>
+        <v>4698.4526999999998</v>
+      </c>
+      <c r="J14" s="66">
+        <v>0</v>
+      </c>
+      <c r="K14" s="67">
+        <f t="shared" si="3"/>
+        <v>46737.660580121999</v>
+      </c>
+      <c r="L14" s="68">
         <f t="shared" si="0"/>
-        <v>156615.09</v>
-      </c>
-      <c r="I14" s="65">
-        <f t="shared" si="1"/>
-        <v>4698.4526999999998</v>
-      </c>
-      <c r="J14" s="66">
-        <v>0</v>
-      </c>
-      <c r="K14" s="67">
-        <f>L$2*D14%</f>
-        <v>46737.660580121999</v>
-      </c>
-      <c r="L14" s="68">
-        <f>ROUND(SUM(H14:K14),0) + O14</f>
         <v>208051.09</v>
       </c>
       <c r="M14" s="69">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>220534.09</v>
       </c>
       <c r="N14" s="70">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>214293.09</v>
       </c>
       <c r="O14" s="39">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0.09</v>
       </c>
       <c r="P14" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="15" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:17" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="57" t="s">
         <v>55</v>
       </c>
@@ -3080,38 +3083,38 @@
       <c r="F15" s="184"/>
       <c r="G15" s="64"/>
       <c r="H15" s="65">
+        <f t="shared" si="1"/>
+        <v>471282.1</v>
+      </c>
+      <c r="I15" s="65">
+        <f t="shared" si="2"/>
+        <v>14138.462999999998</v>
+      </c>
+      <c r="J15" s="66">
+        <v>0</v>
+      </c>
+      <c r="K15" s="67">
+        <f t="shared" si="3"/>
+        <v>99801.180580122018</v>
+      </c>
+      <c r="L15" s="68">
         <f t="shared" si="0"/>
-        <v>471282.1</v>
-      </c>
-      <c r="I15" s="65">
-        <f t="shared" si="1"/>
-        <v>14138.462999999998</v>
-      </c>
-      <c r="J15" s="66">
-        <v>0</v>
-      </c>
-      <c r="K15" s="67">
-        <f>L$2*D15%</f>
-        <v>99801.180580122018</v>
-      </c>
-      <c r="L15" s="68">
-        <f>ROUND(SUM(H15:K15),0) + O15</f>
         <v>585222.1</v>
       </c>
       <c r="M15" s="69">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>620335.1</v>
       </c>
       <c r="N15" s="70">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>602779.1</v>
       </c>
       <c r="O15" s="39">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>9.9999999999999992E-2</v>
       </c>
     </row>
-    <row r="16" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:17" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="57" t="s">
         <v>61</v>
       </c>
@@ -3132,38 +3135,38 @@
       </c>
       <c r="G16" s="64"/>
       <c r="H16" s="65">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I16" s="65">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="J16" s="66">
+        <v>0</v>
+      </c>
+      <c r="K16" s="67">
+        <f t="shared" si="3"/>
+        <v>65530.990580122008</v>
+      </c>
+      <c r="L16" s="68">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I16" s="65">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="J16" s="66">
-        <v>0</v>
-      </c>
-      <c r="K16" s="67">
-        <f>L$2*D16%</f>
-        <v>65530.990580122008</v>
-      </c>
-      <c r="L16" s="68">
-        <f>ROUND(SUM(H16:K16),0) + O16</f>
         <v>65531.11</v>
       </c>
       <c r="M16" s="69">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>69463.11</v>
       </c>
       <c r="N16" s="70">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>67497.11</v>
       </c>
       <c r="O16" s="39">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0.10999999999999999</v>
       </c>
     </row>
-    <row r="17" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:16" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="57" t="s">
         <v>62</v>
       </c>
@@ -3181,38 +3184,38 @@
       <c r="F17" s="184"/>
       <c r="G17" s="64"/>
       <c r="H17" s="65">
+        <f t="shared" si="1"/>
+        <v>99546.12</v>
+      </c>
+      <c r="I17" s="65">
+        <f t="shared" si="2"/>
+        <v>2986.3835999999997</v>
+      </c>
+      <c r="J17" s="66">
+        <v>0</v>
+      </c>
+      <c r="K17" s="67">
+        <f t="shared" si="3"/>
+        <v>46737.660580121999</v>
+      </c>
+      <c r="L17" s="68">
         <f t="shared" si="0"/>
-        <v>99546.12</v>
-      </c>
-      <c r="I17" s="65">
-        <f t="shared" si="1"/>
-        <v>2986.3835999999997</v>
-      </c>
-      <c r="J17" s="66">
-        <v>0</v>
-      </c>
-      <c r="K17" s="67">
-        <f>L$2*D17%</f>
-        <v>46737.660580121999</v>
-      </c>
-      <c r="L17" s="68">
-        <f>ROUND(SUM(H17:K17),0) + O17</f>
         <v>149270.12</v>
       </c>
       <c r="M17" s="69">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>158226.12</v>
       </c>
       <c r="N17" s="70">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>153748.12</v>
       </c>
       <c r="O17" s="39">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0.11999999999999998</v>
       </c>
     </row>
-    <row r="18" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:16" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="57" t="s">
         <v>60</v>
       </c>
@@ -3233,36 +3236,36 @@
       </c>
       <c r="G18" s="64"/>
       <c r="H18" s="65">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>674184.06</v>
       </c>
       <c r="I18" s="65">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>20225.521800000002</v>
       </c>
       <c r="J18" s="66"/>
       <c r="K18" s="67">
-        <f>L$2*D18%</f>
+        <f t="shared" si="3"/>
         <v>134071.37058012199</v>
       </c>
       <c r="L18" s="68">
-        <f>ROUND(SUM(H18:K18),0) + O18</f>
+        <f t="shared" si="0"/>
         <v>828481.13</v>
       </c>
       <c r="M18" s="69"/>
       <c r="N18" s="70">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>853335.13</v>
       </c>
       <c r="O18" s="39">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0.12999999999999998</v>
       </c>
       <c r="P18" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="19" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:16" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="57"/>
       <c r="B19" s="57"/>
       <c r="C19" s="58"/>
@@ -3278,11 +3281,11 @@
       <c r="M19" s="69"/>
       <c r="N19" s="70"/>
       <c r="O19" s="39">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0.13999999999999999</v>
       </c>
     </row>
-    <row r="20" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:16" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="57" t="s">
         <v>63</v>
       </c>
@@ -3300,11 +3303,11 @@
       <c r="F20" s="184"/>
       <c r="G20" s="64"/>
       <c r="H20" s="65">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>43759.15</v>
       </c>
       <c r="I20" s="65">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1312.7745</v>
       </c>
       <c r="J20" s="66"/>
@@ -3318,15 +3321,15 @@
       </c>
       <c r="M20" s="69"/>
       <c r="N20" s="70">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>71791.149999999994</v>
       </c>
       <c r="O20" s="39">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0.15</v>
       </c>
     </row>
-    <row r="21" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:16" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="57" t="s">
         <v>64</v>
       </c>
@@ -3344,11 +3347,11 @@
       <c r="F21" s="184"/>
       <c r="G21" s="64"/>
       <c r="H21" s="65">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>43759.16</v>
       </c>
       <c r="I21" s="65">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1312.7748000000001</v>
       </c>
       <c r="J21" s="66"/>
@@ -3362,18 +3365,18 @@
       </c>
       <c r="M21" s="69"/>
       <c r="N21" s="70">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>71791.16</v>
       </c>
       <c r="O21" s="39">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0.16</v>
       </c>
       <c r="P21" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="22" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:16" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="57" t="s">
         <v>65</v>
       </c>
@@ -3391,11 +3394,11 @@
       <c r="F22" s="184"/>
       <c r="G22" s="64"/>
       <c r="H22" s="65">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>51678.17</v>
       </c>
       <c r="I22" s="65">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1550.3451</v>
       </c>
       <c r="J22" s="66"/>
@@ -3409,15 +3412,15 @@
       </c>
       <c r="M22" s="69"/>
       <c r="N22" s="70">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>80192.17</v>
       </c>
       <c r="O22" s="39">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0.17</v>
       </c>
     </row>
-    <row r="23" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:16" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="57" t="s">
         <v>66</v>
       </c>
@@ -3435,11 +3438,11 @@
       <c r="F23" s="184"/>
       <c r="G23" s="64"/>
       <c r="H23" s="65">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>43759.18</v>
       </c>
       <c r="I23" s="65">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1312.7754</v>
       </c>
       <c r="J23" s="66"/>
@@ -3453,15 +3456,15 @@
       </c>
       <c r="M23" s="69"/>
       <c r="N23" s="70">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>71791.179999999993</v>
       </c>
       <c r="O23" s="39">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0.18000000000000002</v>
       </c>
     </row>
-    <row r="24" spans="1:16" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:16" ht="17.149999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A24" s="57" t="s">
         <v>67</v>
       </c>
@@ -3479,11 +3482,11 @@
       <c r="F24" s="184"/>
       <c r="G24" s="64"/>
       <c r="H24" s="65">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>51678.19</v>
       </c>
       <c r="I24" s="65">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1550.3457000000001</v>
       </c>
       <c r="J24" s="66">
@@ -3498,135 +3501,128 @@
         <v>77856.19</v>
       </c>
       <c r="M24" s="69">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>82528.19</v>
       </c>
       <c r="N24" s="70">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>80192.19</v>
       </c>
       <c r="O24" s="39">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0.19000000000000003</v>
       </c>
     </row>
-    <row r="25" spans="1:16" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:16" ht="17.149999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A25" s="71"/>
       <c r="B25" s="72"/>
       <c r="C25" s="72"/>
       <c r="D25" s="73">
-        <f t="shared" ref="D25:N25" si="5">SUM(D6:D24)</f>
+        <f t="shared" ref="D25:N25" si="7">SUM(D6:D24)</f>
         <v>100.00000003999999</v>
       </c>
       <c r="E25" s="47">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>3763785.7600000002</v>
       </c>
       <c r="F25" s="55">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>986668.29</v>
       </c>
       <c r="G25" s="47">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="H25" s="55">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>2777117.4700000007</v>
       </c>
       <c r="I25" s="55">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>83313.52410000001</v>
       </c>
       <c r="J25" s="55">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="K25" s="102">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>1105490.0004421964</v>
       </c>
       <c r="L25" s="74">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>3965922.7600000002</v>
       </c>
       <c r="M25" s="74">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>3021513.97</v>
       </c>
       <c r="N25" s="74">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>4084901.7600000002</v>
       </c>
     </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:16" x14ac:dyDescent="0.35">
       <c r="B26" s="46"/>
       <c r="C26" s="46"/>
       <c r="D26" s="116"/>
     </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="B27" s="191" t="s">
+    <row r="27" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="B27" s="192" t="s">
         <v>85</v>
       </c>
-      <c r="C27" s="191"/>
-      <c r="D27" s="191"/>
-      <c r="E27" s="191"/>
-      <c r="F27" s="191"/>
-      <c r="G27" s="191"/>
-      <c r="H27" s="191"/>
-      <c r="I27" s="191"/>
-      <c r="J27" s="191"/>
-      <c r="K27" s="191"/>
-      <c r="L27" s="191"/>
-    </row>
-    <row r="28" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="B28" s="191"/>
-      <c r="C28" s="191"/>
-      <c r="D28" s="191"/>
-      <c r="E28" s="191"/>
-      <c r="F28" s="191"/>
-      <c r="G28" s="191"/>
-      <c r="H28" s="191"/>
-      <c r="I28" s="191"/>
-      <c r="J28" s="191"/>
-      <c r="K28" s="191"/>
-      <c r="L28" s="191"/>
-    </row>
-    <row r="29" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="B29" s="191"/>
-      <c r="C29" s="191"/>
-      <c r="D29" s="191"/>
-      <c r="E29" s="191"/>
-      <c r="F29" s="191"/>
-      <c r="G29" s="191"/>
-      <c r="H29" s="191"/>
-      <c r="I29" s="191"/>
-      <c r="J29" s="191"/>
-      <c r="K29" s="191"/>
-      <c r="L29" s="191"/>
-    </row>
-    <row r="30" spans="1:16" ht="72" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B30" s="191"/>
-      <c r="C30" s="191"/>
-      <c r="D30" s="191"/>
-      <c r="E30" s="191"/>
-      <c r="F30" s="191"/>
-      <c r="G30" s="191"/>
-      <c r="H30" s="191"/>
-      <c r="I30" s="191"/>
-      <c r="J30" s="191"/>
-      <c r="K30" s="191"/>
-      <c r="L30" s="191"/>
+      <c r="C27" s="192"/>
+      <c r="D27" s="192"/>
+      <c r="E27" s="192"/>
+      <c r="F27" s="192"/>
+      <c r="G27" s="192"/>
+      <c r="H27" s="192"/>
+      <c r="I27" s="192"/>
+      <c r="J27" s="192"/>
+      <c r="K27" s="192"/>
+      <c r="L27" s="192"/>
+    </row>
+    <row r="28" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="B28" s="192"/>
+      <c r="C28" s="192"/>
+      <c r="D28" s="192"/>
+      <c r="E28" s="192"/>
+      <c r="F28" s="192"/>
+      <c r="G28" s="192"/>
+      <c r="H28" s="192"/>
+      <c r="I28" s="192"/>
+      <c r="J28" s="192"/>
+      <c r="K28" s="192"/>
+      <c r="L28" s="192"/>
+    </row>
+    <row r="29" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="B29" s="192"/>
+      <c r="C29" s="192"/>
+      <c r="D29" s="192"/>
+      <c r="E29" s="192"/>
+      <c r="F29" s="192"/>
+      <c r="G29" s="192"/>
+      <c r="H29" s="192"/>
+      <c r="I29" s="192"/>
+      <c r="J29" s="192"/>
+      <c r="K29" s="192"/>
+      <c r="L29" s="192"/>
+    </row>
+    <row r="30" spans="1:16" ht="72" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B30" s="192"/>
+      <c r="C30" s="192"/>
+      <c r="D30" s="192"/>
+      <c r="E30" s="192"/>
+      <c r="F30" s="192"/>
+      <c r="G30" s="192"/>
+      <c r="H30" s="192"/>
+      <c r="I30" s="192"/>
+      <c r="J30" s="192"/>
+      <c r="K30" s="192"/>
+      <c r="L30" s="192"/>
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="D4:D5"/>
-    <mergeCell ref="I4:I5"/>
-    <mergeCell ref="E4:E5"/>
-    <mergeCell ref="F4:F5"/>
-    <mergeCell ref="H4:H5"/>
     <mergeCell ref="B2:H3"/>
     <mergeCell ref="N4:N5"/>
     <mergeCell ref="B27:L30"/>
@@ -3635,6 +3631,13 @@
     <mergeCell ref="M4:M5"/>
     <mergeCell ref="J4:J5"/>
     <mergeCell ref="K4:K5"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="D4:D5"/>
+    <mergeCell ref="I4:I5"/>
+    <mergeCell ref="E4:E5"/>
+    <mergeCell ref="F4:F5"/>
+    <mergeCell ref="H4:H5"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>
@@ -3644,41 +3647,41 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{642D1833-D35F-45AC-9D7A-9C6C07C828FD}">
   <dimension ref="A1:Q32"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="5" hidden="1" customWidth="1"/>
-    <col min="2" max="2" width="8.33203125" hidden="1" customWidth="1"/>
-    <col min="3" max="3" width="7.5546875" customWidth="1"/>
-    <col min="4" max="4" width="23.6640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.36328125" hidden="1" customWidth="1"/>
+    <col min="3" max="3" width="7.54296875" customWidth="1"/>
+    <col min="4" max="4" width="23.6328125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.54296875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="12" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8.33203125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="7.33203125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="12.44140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.36328125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="7.36328125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.453125" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="8" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="11.33203125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="8.6640625" customWidth="1"/>
-    <col min="13" max="13" width="11.44140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.36328125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8.6328125" customWidth="1"/>
+    <col min="13" max="13" width="11.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="211" t="s">
+    <row r="1" spans="1:17" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="212" t="s">
         <v>69</v>
       </c>
-      <c r="B1" s="212"/>
-      <c r="C1" s="212"/>
-      <c r="D1" s="212"/>
-      <c r="E1" s="212"/>
-      <c r="F1" s="212"/>
-      <c r="G1" s="212"/>
-      <c r="H1" s="212"/>
-      <c r="I1" s="212"/>
-      <c r="J1" s="212"/>
-      <c r="K1" s="212"/>
-      <c r="L1" s="212"/>
-      <c r="M1" s="213"/>
-    </row>
-    <row r="2" spans="1:17" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B1" s="213"/>
+      <c r="C1" s="213"/>
+      <c r="D1" s="213"/>
+      <c r="E1" s="213"/>
+      <c r="F1" s="213"/>
+      <c r="G1" s="213"/>
+      <c r="H1" s="213"/>
+      <c r="I1" s="213"/>
+      <c r="J1" s="213"/>
+      <c r="K1" s="213"/>
+      <c r="L1" s="213"/>
+      <c r="M1" s="214"/>
+    </row>
+    <row r="2" spans="1:17" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="123"/>
       <c r="B2" s="123" t="s">
         <v>69</v>
@@ -3698,30 +3701,30 @@
       <c r="M2" s="118"/>
       <c r="N2" s="121"/>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A3" s="123"/>
       <c r="B3" s="122" t="s">
         <v>69</v>
       </c>
-      <c r="C3" s="216">
-        <v>0</v>
-      </c>
-      <c r="D3" s="216"/>
+      <c r="C3" s="217">
+        <v>0</v>
+      </c>
+      <c r="D3" s="217"/>
       <c r="E3" s="125"/>
       <c r="F3" s="125"/>
       <c r="G3" s="125"/>
       <c r="H3" s="126"/>
       <c r="I3" s="120"/>
       <c r="J3" s="127"/>
-      <c r="K3" s="214">
+      <c r="K3" s="215">
         <f>D2-I24</f>
         <v>858773.02</v>
       </c>
-      <c r="L3" s="214"/>
+      <c r="L3" s="215"/>
       <c r="M3" s="128"/>
       <c r="N3" s="121"/>
     </row>
-    <row r="4" spans="1:17" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:17" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="129" t="s">
         <v>70</v>
       </c>
@@ -3763,7 +3766,7 @@
       </c>
       <c r="N4" s="121"/>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A5" s="136">
         <v>1</v>
       </c>
@@ -3813,7 +3816,7 @@
       </c>
       <c r="N5" s="121"/>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A6" s="146">
         <v>2</v>
       </c>
@@ -3863,7 +3866,7 @@
       </c>
       <c r="N6" s="121"/>
     </row>
-    <row r="7" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="136">
         <v>3</v>
       </c>
@@ -3916,7 +3919,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A8" s="136">
         <v>4</v>
       </c>
@@ -3966,7 +3969,7 @@
       </c>
       <c r="N8" s="121"/>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A9" s="136">
         <v>6</v>
       </c>
@@ -4016,7 +4019,7 @@
       </c>
       <c r="N9" s="121"/>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A10" s="136">
         <v>7</v>
       </c>
@@ -4065,7 +4068,7 @@
         <v>196313.01492019495</v>
       </c>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A11" s="136">
         <v>8</v>
       </c>
@@ -4114,7 +4117,7 @@
         <v>79981.119880194965</v>
       </c>
     </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A12" s="136">
         <v>9</v>
       </c>
@@ -4163,7 +4166,7 @@
         <v>220779.15626019496</v>
       </c>
     </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A13" s="136">
         <v>10</v>
       </c>
@@ -4212,7 +4215,7 @@
         <v>110315.01492019495</v>
       </c>
     </row>
-    <row r="14" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="136">
         <v>11</v>
       </c>
@@ -4261,7 +4264,7 @@
         <v>371481.11988019495</v>
       </c>
     </row>
-    <row r="15" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="136">
         <v>12</v>
       </c>
@@ -4310,7 +4313,7 @@
         <v>113232.15626019496</v>
       </c>
     </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A16" s="136">
         <v>13</v>
       </c>
@@ -4359,7 +4362,7 @@
         <v>37781.014920194961</v>
       </c>
     </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A17" s="136">
         <v>14</v>
       </c>
@@ -4408,7 +4411,7 @@
         <v>647935.08350019495</v>
       </c>
     </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A18" s="136">
         <v>15</v>
       </c>
@@ -4427,7 +4430,7 @@
       <c r="L18" s="144"/>
       <c r="M18" s="142"/>
     </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A19" s="136">
         <v>16</v>
       </c>
@@ -4476,7 +4479,7 @@
         <v>19131.554520194957</v>
       </c>
     </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A20" s="136">
         <v>17</v>
       </c>
@@ -4525,7 +4528,7 @@
         <v>19131.554520194957</v>
       </c>
     </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A21" s="136">
         <v>18</v>
       </c>
@@ -4574,7 +4577,7 @@
         <v>19131.554520194957</v>
       </c>
     </row>
-    <row r="22" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="136">
         <v>19</v>
       </c>
@@ -4616,7 +4619,7 @@
         <v>19131.554520194957</v>
       </c>
     </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A23" s="136">
         <v>20</v>
       </c>
@@ -4655,7 +4658,7 @@
         <v>19131.554520194957</v>
       </c>
     </row>
-    <row r="24" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="136">
         <v>24</v>
       </c>
@@ -4685,7 +4688,7 @@
       </c>
       <c r="N24" s="39"/>
     </row>
-    <row r="25" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A25" s="120"/>
       <c r="C25" s="157"/>
       <c r="D25" s="158"/>
@@ -4705,39 +4708,39 @@
       <c r="L25" s="160"/>
       <c r="M25" s="160"/>
     </row>
-    <row r="26" spans="1:14" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:14" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A26" s="165" t="s">
         <v>80</v>
       </c>
-      <c r="C26" s="215"/>
-      <c r="D26" s="212"/>
-      <c r="E26" s="212"/>
-      <c r="F26" s="212"/>
-      <c r="G26" s="212"/>
-      <c r="H26" s="212"/>
-      <c r="I26" s="212"/>
-      <c r="J26" s="212"/>
-      <c r="K26" s="212"/>
-      <c r="L26" s="212"/>
-      <c r="M26" s="212"/>
-    </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="C26" s="216"/>
+      <c r="D26" s="213"/>
+      <c r="E26" s="213"/>
+      <c r="F26" s="213"/>
+      <c r="G26" s="213"/>
+      <c r="H26" s="213"/>
+      <c r="I26" s="213"/>
+      <c r="J26" s="213"/>
+      <c r="K26" s="213"/>
+      <c r="L26" s="213"/>
+      <c r="M26" s="213"/>
+    </row>
+    <row r="27" spans="1:14" x14ac:dyDescent="0.35">
       <c r="H27" s="164"/>
       <c r="I27" s="166"/>
       <c r="J27" s="166"/>
       <c r="K27" s="166"/>
       <c r="M27" s="145"/>
     </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:14" x14ac:dyDescent="0.35">
       <c r="E29" s="2"/>
     </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:14" x14ac:dyDescent="0.35">
       <c r="K30" s="167"/>
     </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:14" x14ac:dyDescent="0.35">
       <c r="K31" s="166"/>
     </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:14" x14ac:dyDescent="0.35">
       <c r="E32" s="168"/>
       <c r="F32" s="168"/>
       <c r="G32" s="168"/>
